--- a/public/StageTable.xlsx
+++ b/public/StageTable.xlsx
@@ -167,9 +167,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="ç­çº¿ Light"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã§Â­ÂÃ§ÂºÂ¿ Light"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -202,9 +202,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="ç­çº¿"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã§Â­ÂÃ§ÂºÂ¿"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -403,7 +403,7 @@
     <col min="22" max="22" customWidth="1" width="11.75"/>
     <col min="23" max="23" customWidth="1" width="11.75"/>
     <col min="24" max="24" customWidth="1" width="11.75"/>
-    <col min="25" max="25" customWidth="1" width="20.8303571428571"/>
+    <col min="25" max="25" customWidth="1" width="20.8333333333333"/>
     <col min="26" max="26" customWidth="1" width="11.75"/>
     <col min="27" max="27" customWidth="1" width="11.75"/>
     <col min="28" max="28" customWidth="1" width="11.75"/>
@@ -16936,10 +16936,10 @@
         <v>long</v>
       </c>
       <c r="V3" t="str">
-        <v>int</v>
+        <v>float</v>
       </c>
       <c r="W3" t="str">
-        <v>int</v>
+        <v>float</v>
       </c>
       <c r="X3" t="str">
         <v>long</v>

--- a/public/StageTable.xlsx
+++ b/public/StageTable.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -812,6 +808,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V5">
+        <f>Y5/100</f>
         <v>1</v>
       </c>
       <c r="W5">
@@ -910,6 +907,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V6">
+        <f>Y6/100</f>
         <v>1</v>
       </c>
       <c r="W6">
@@ -1008,6 +1006,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V7">
+        <f>Y7/100</f>
         <v>1</v>
       </c>
       <c r="W7">
@@ -1106,6 +1105,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V8">
+        <f>Y8/100</f>
         <v>1</v>
       </c>
       <c r="W8">
@@ -1204,6 +1204,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V9">
+        <f>Y9/100</f>
         <v>1</v>
       </c>
       <c r="W9">
@@ -1302,6 +1303,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V10">
+        <f>Y10/100</f>
         <v>1</v>
       </c>
       <c r="W10">
@@ -1400,6 +1402,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V11">
+        <f>Y11/100</f>
         <v>1</v>
       </c>
       <c r="W11">
@@ -1498,6 +1501,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V12">
+        <f>Y12/100</f>
         <v>1</v>
       </c>
       <c r="W12">
@@ -1596,6 +1600,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V13">
+        <f>Y13/100</f>
         <v>1</v>
       </c>
       <c r="W13">
@@ -1694,6 +1699,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V14">
+        <f>Y14/100</f>
         <v>1.43</v>
       </c>
       <c r="W14">
@@ -1792,6 +1798,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V15">
+        <f>Y15/100</f>
         <v>1.1</v>
       </c>
       <c r="W15">
@@ -1890,6 +1897,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V16">
+        <f>Y16/100</f>
         <v>1.1</v>
       </c>
       <c r="W16">
@@ -1988,6 +1996,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V17">
+        <f>Y17/100</f>
         <v>1.1</v>
       </c>
       <c r="W17">
@@ -2086,6 +2095,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V18">
+        <f>Y18/100</f>
         <v>1.1</v>
       </c>
       <c r="W18">
@@ -2184,6 +2194,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V19">
+        <f>Y19/100</f>
         <v>1.1</v>
       </c>
       <c r="W19">
@@ -2282,6 +2293,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V20">
+        <f>Y20/100</f>
         <v>1.1</v>
       </c>
       <c r="W20">
@@ -2380,6 +2392,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V21">
+        <f>Y21/100</f>
         <v>1.1</v>
       </c>
       <c r="W21">
@@ -2478,6 +2491,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V22">
+        <f>Y22/100</f>
         <v>1.1</v>
       </c>
       <c r="W22">
@@ -2576,6 +2590,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V23">
+        <f>Y23/100</f>
         <v>1.1</v>
       </c>
       <c r="W23">
@@ -2674,6 +2689,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V24">
+        <f>Y24/100</f>
         <v>1.57</v>
       </c>
       <c r="W24">
@@ -2772,6 +2788,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V25">
+        <f>Y25/100</f>
         <v>1.21</v>
       </c>
       <c r="W25">
@@ -2870,6 +2887,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V26">
+        <f>Y26/100</f>
         <v>1.21</v>
       </c>
       <c r="W26">
@@ -2968,6 +2986,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V27">
+        <f>Y27/100</f>
         <v>1.21</v>
       </c>
       <c r="W27">
@@ -3066,6 +3085,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V28">
+        <f>Y28/100</f>
         <v>1.21</v>
       </c>
       <c r="W28">
@@ -3164,6 +3184,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V29">
+        <f>Y29/100</f>
         <v>1.21</v>
       </c>
       <c r="W29">
@@ -3262,6 +3283,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V30">
+        <f>Y30/100</f>
         <v>1.21</v>
       </c>
       <c r="W30">
@@ -3360,6 +3382,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V31">
+        <f>Y31/100</f>
         <v>1.21</v>
       </c>
       <c r="W31">
@@ -3458,6 +3481,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V32">
+        <f>Y32/100</f>
         <v>1.21</v>
       </c>
       <c r="W32">
@@ -3556,6 +3580,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V33">
+        <f>Y33/100</f>
         <v>1.21</v>
       </c>
       <c r="W33">
@@ -3654,6 +3679,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V34">
+        <f>Y34/100</f>
         <v>1.73</v>
       </c>
       <c r="W34">
@@ -3752,6 +3778,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V35">
+        <f>Y35/100</f>
         <v>1.33</v>
       </c>
       <c r="W35">
@@ -3850,6 +3877,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V36">
+        <f>Y36/100</f>
         <v>1.33</v>
       </c>
       <c r="W36">
@@ -3948,6 +3976,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V37">
+        <f>Y37/100</f>
         <v>1.33</v>
       </c>
       <c r="W37">
@@ -4046,6 +4075,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V38">
+        <f>Y38/100</f>
         <v>1.33</v>
       </c>
       <c r="W38">
@@ -4144,6 +4174,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V39">
+        <f>Y39/100</f>
         <v>1.33</v>
       </c>
       <c r="W39">
@@ -4242,6 +4273,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V40">
+        <f>Y40/100</f>
         <v>1.33</v>
       </c>
       <c r="W40">
@@ -4340,6 +4372,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V41">
+        <f>Y41/100</f>
         <v>1.33</v>
       </c>
       <c r="W41">
@@ -4438,6 +4471,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V42">
+        <f>Y42/100</f>
         <v>1.33</v>
       </c>
       <c r="W42">
@@ -4536,6 +4570,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V43">
+        <f>Y43/100</f>
         <v>1.33</v>
       </c>
       <c r="W43">
@@ -4634,6 +4669,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V44">
+        <f>Y44/100</f>
         <v>1.9</v>
       </c>
       <c r="W44">
@@ -4732,6 +4768,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V45">
+        <f>Y45/100</f>
         <v>1.46</v>
       </c>
       <c r="W45">
@@ -4830,6 +4867,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V46">
+        <f>Y46/100</f>
         <v>1.46</v>
       </c>
       <c r="W46">
@@ -4928,6 +4966,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V47">
+        <f>Y47/100</f>
         <v>1.46</v>
       </c>
       <c r="W47">
@@ -5026,6 +5065,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V48">
+        <f>Y48/100</f>
         <v>1.46</v>
       </c>
       <c r="W48">
@@ -5124,6 +5164,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V49">
+        <f>Y49/100</f>
         <v>1.46</v>
       </c>
       <c r="W49">
@@ -5222,6 +5263,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V50">
+        <f>Y50/100</f>
         <v>1.46</v>
       </c>
       <c r="W50">
@@ -5320,6 +5362,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V51">
+        <f>Y51/100</f>
         <v>1.46</v>
       </c>
       <c r="W51">
@@ -5418,6 +5461,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V52">
+        <f>Y52/100</f>
         <v>1.46</v>
       </c>
       <c r="W52">
@@ -5516,6 +5560,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V53">
+        <f>Y53/100</f>
         <v>1.46</v>
       </c>
       <c r="W53">
@@ -5614,6 +5659,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V54">
+        <f>Y54/100</f>
         <v>2.58</v>
       </c>
       <c r="W54">
@@ -5712,6 +5758,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V55">
+        <f>Y55/100</f>
         <v>1.61</v>
       </c>
       <c r="W55">
@@ -5810,6 +5857,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V56">
+        <f>Y56/100</f>
         <v>1.61</v>
       </c>
       <c r="W56">
@@ -5908,6 +5956,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V57">
+        <f>Y57/100</f>
         <v>1.61</v>
       </c>
       <c r="W57">
@@ -6006,6 +6055,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V58">
+        <f>Y58/100</f>
         <v>1.61</v>
       </c>
       <c r="W58">
@@ -6104,6 +6154,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V59">
+        <f>Y59/100</f>
         <v>1.61</v>
       </c>
       <c r="W59">
@@ -6202,6 +6253,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V60">
+        <f>Y60/100</f>
         <v>1.61</v>
       </c>
       <c r="W60">
@@ -6300,6 +6352,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V61">
+        <f>Y61/100</f>
         <v>1.61</v>
       </c>
       <c r="W61">
@@ -6398,6 +6451,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V62">
+        <f>Y62/100</f>
         <v>1.61</v>
       </c>
       <c r="W62">
@@ -6496,6 +6550,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V63">
+        <f>Y63/100</f>
         <v>1.61</v>
       </c>
       <c r="W63">
@@ -6594,6 +6649,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V64">
+        <f>Y64/100</f>
         <v>2.3</v>
       </c>
       <c r="W64">
@@ -6692,6 +6748,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V65">
+        <f>Y65/100</f>
         <v>1.77</v>
       </c>
       <c r="W65">
@@ -6790,6 +6847,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V66">
+        <f>Y66/100</f>
         <v>1.77</v>
       </c>
       <c r="W66">
@@ -6888,6 +6946,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V67">
+        <f>Y67/100</f>
         <v>1.77</v>
       </c>
       <c r="W67">
@@ -6986,6 +7045,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V68">
+        <f>Y68/100</f>
         <v>1.77</v>
       </c>
       <c r="W68">
@@ -7084,6 +7144,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V69">
+        <f>Y69/100</f>
         <v>1.77</v>
       </c>
       <c r="W69">
@@ -7182,6 +7243,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V70">
+        <f>Y70/100</f>
         <v>1.77</v>
       </c>
       <c r="W70">
@@ -7280,6 +7342,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V71">
+        <f>Y71/100</f>
         <v>1.77</v>
       </c>
       <c r="W71">
@@ -7378,6 +7441,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V72">
+        <f>Y72/100</f>
         <v>1.77</v>
       </c>
       <c r="W72">
@@ -7476,6 +7540,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V73">
+        <f>Y73/100</f>
         <v>1.77</v>
       </c>
       <c r="W73">
@@ -7574,6 +7639,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V74">
+        <f>Y74/100</f>
         <v>2.53</v>
       </c>
       <c r="W74">
@@ -7672,6 +7738,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V75">
+        <f>Y75/100</f>
         <v>1.95</v>
       </c>
       <c r="W75">
@@ -7770,6 +7837,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V76">
+        <f>Y76/100</f>
         <v>1.95</v>
       </c>
       <c r="W76">
@@ -7868,6 +7936,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V77">
+        <f>Y77/100</f>
         <v>1.95</v>
       </c>
       <c r="W77">
@@ -7966,6 +8035,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V78">
+        <f>Y78/100</f>
         <v>1.95</v>
       </c>
       <c r="W78">
@@ -8064,6 +8134,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V79">
+        <f>Y79/100</f>
         <v>1.95</v>
       </c>
       <c r="W79">
@@ -8162,6 +8233,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V80">
+        <f>Y80/100</f>
         <v>1.95</v>
       </c>
       <c r="W80">
@@ -8260,6 +8332,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V81">
+        <f>Y81/100</f>
         <v>1.95</v>
       </c>
       <c r="W81">
@@ -8358,6 +8431,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V82">
+        <f>Y82/100</f>
         <v>1.95</v>
       </c>
       <c r="W82">
@@ -8456,6 +8530,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V83">
+        <f>Y83/100</f>
         <v>1.95</v>
       </c>
       <c r="W83">
@@ -8554,6 +8629,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V84">
+        <f>Y84/100</f>
         <v>2.79</v>
       </c>
       <c r="W84">
@@ -8652,6 +8728,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V85">
+        <f>Y85/100</f>
         <v>2.14</v>
       </c>
       <c r="W85">
@@ -8750,6 +8827,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V86">
+        <f>Y86/100</f>
         <v>2.14</v>
       </c>
       <c r="W86">
@@ -8848,6 +8926,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V87">
+        <f>Y87/100</f>
         <v>2.14</v>
       </c>
       <c r="W87">
@@ -8946,6 +9025,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V88">
+        <f>Y88/100</f>
         <v>2.14</v>
       </c>
       <c r="W88">
@@ -9044,6 +9124,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V89">
+        <f>Y89/100</f>
         <v>2.14</v>
       </c>
       <c r="W89">
@@ -9142,6 +9223,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V90">
+        <f>Y90/100</f>
         <v>2.14</v>
       </c>
       <c r="W90">
@@ -9240,6 +9322,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V91">
+        <f>Y91/100</f>
         <v>2.14</v>
       </c>
       <c r="W91">
@@ -9338,6 +9421,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V92">
+        <f>Y92/100</f>
         <v>2.14</v>
       </c>
       <c r="W92">
@@ -9436,6 +9520,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V93">
+        <f>Y93/100</f>
         <v>2.14</v>
       </c>
       <c r="W93">
@@ -9534,6 +9619,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V94">
+        <f>Y94/100</f>
         <v>3.07</v>
       </c>
       <c r="W94">
@@ -9632,6 +9718,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V95">
+        <f>Y95/100</f>
         <v>2.36</v>
       </c>
       <c r="W95">
@@ -9730,6 +9817,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V96">
+        <f>Y96/100</f>
         <v>2.36</v>
       </c>
       <c r="W96">
@@ -9828,6 +9916,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V97">
+        <f>Y97/100</f>
         <v>2.36</v>
       </c>
       <c r="W97">
@@ -9926,6 +10015,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V98">
+        <f>Y98/100</f>
         <v>2.36</v>
       </c>
       <c r="W98">
@@ -10024,6 +10114,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V99">
+        <f>Y99/100</f>
         <v>2.36</v>
       </c>
       <c r="W99">
@@ -10122,6 +10213,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V100">
+        <f>Y100/100</f>
         <v>2.36</v>
       </c>
       <c r="W100">
@@ -10220,6 +10312,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V101">
+        <f>Y101/100</f>
         <v>2.36</v>
       </c>
       <c r="W101">
@@ -10318,6 +10411,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V102">
+        <f>Y102/100</f>
         <v>2.36</v>
       </c>
       <c r="W102">
@@ -10416,6 +10510,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V103">
+        <f>Y103/100</f>
         <v>2.36</v>
       </c>
       <c r="W103">
@@ -10514,6 +10609,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V104">
+        <f>Y104/100</f>
         <v>4.15</v>
       </c>
       <c r="W104">
@@ -10612,6 +10708,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V105">
+        <f>Y105/100</f>
         <v>2.59</v>
       </c>
       <c r="W105">
@@ -10710,6 +10807,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V106">
+        <f>Y106/100</f>
         <v>2.59</v>
       </c>
       <c r="W106">
@@ -10808,6 +10906,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V107">
+        <f>Y107/100</f>
         <v>2.59</v>
       </c>
       <c r="W107">
@@ -10906,6 +11005,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V108">
+        <f>Y108/100</f>
         <v>2.59</v>
       </c>
       <c r="W108">
@@ -11004,6 +11104,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V109">
+        <f>Y109/100</f>
         <v>2.59</v>
       </c>
       <c r="W109">
@@ -11102,6 +11203,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V110">
+        <f>Y110/100</f>
         <v>2.59</v>
       </c>
       <c r="W110">
@@ -11200,6 +11302,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V111">
+        <f>Y111/100</f>
         <v>2.59</v>
       </c>
       <c r="W111">
@@ -11298,6 +11401,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V112">
+        <f>Y112/100</f>
         <v>2.59</v>
       </c>
       <c r="W112">
@@ -11396,6 +11500,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V113">
+        <f>Y113/100</f>
         <v>2.59</v>
       </c>
       <c r="W113">
@@ -11494,6 +11599,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V114">
+        <f>Y114/100</f>
         <v>3.71</v>
       </c>
       <c r="W114">
@@ -11592,6 +11698,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V115">
+        <f>Y115/100</f>
         <v>2.85</v>
       </c>
       <c r="W115">
@@ -11690,6 +11797,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V116">
+        <f>Y116/100</f>
         <v>2.85</v>
       </c>
       <c r="W116">
@@ -11788,6 +11896,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V117">
+        <f>Y117/100</f>
         <v>2.85</v>
       </c>
       <c r="W117">
@@ -11886,6 +11995,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V118">
+        <f>Y118/100</f>
         <v>2.85</v>
       </c>
       <c r="W118">
@@ -11984,6 +12094,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V119">
+        <f>Y119/100</f>
         <v>2.85</v>
       </c>
       <c r="W119">
@@ -12082,6 +12193,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V120">
+        <f>Y120/100</f>
         <v>2.85</v>
       </c>
       <c r="W120">
@@ -12180,6 +12292,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V121">
+        <f>Y121/100</f>
         <v>2.85</v>
       </c>
       <c r="W121">
@@ -12278,6 +12391,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V122">
+        <f>Y122/100</f>
         <v>2.85</v>
       </c>
       <c r="W122">
@@ -12376,6 +12490,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V123">
+        <f>Y123/100</f>
         <v>2.85</v>
       </c>
       <c r="W123">
@@ -12474,6 +12589,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V124">
+        <f>Y124/100</f>
         <v>4.08</v>
       </c>
       <c r="W124">
@@ -12572,6 +12688,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V125">
+        <f>Y125/100</f>
         <v>3.14</v>
       </c>
       <c r="W125">
@@ -12670,6 +12787,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V126">
+        <f>Y126/100</f>
         <v>3.14</v>
       </c>
       <c r="W126">
@@ -12768,6 +12886,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V127">
+        <f>Y127/100</f>
         <v>3.14</v>
       </c>
       <c r="W127">
@@ -12866,6 +12985,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V128">
+        <f>Y128/100</f>
         <v>3.14</v>
       </c>
       <c r="W128">
@@ -12964,6 +13084,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V129">
+        <f>Y129/100</f>
         <v>3.14</v>
       </c>
       <c r="W129">
@@ -13062,6 +13183,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V130">
+        <f>Y130/100</f>
         <v>3.14</v>
       </c>
       <c r="W130">
@@ -13160,6 +13282,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V131">
+        <f>Y131/100</f>
         <v>3.14</v>
       </c>
       <c r="W131">
@@ -13258,6 +13381,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V132">
+        <f>Y132/100</f>
         <v>3.14</v>
       </c>
       <c r="W132">
@@ -13356,6 +13480,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V133">
+        <f>Y133/100</f>
         <v>3.14</v>
       </c>
       <c r="W133">
@@ -13454,6 +13579,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V134">
+        <f>Y134/100</f>
         <v>4.49</v>
       </c>
       <c r="W134">
@@ -13552,6 +13678,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V135">
+        <f>Y135/100</f>
         <v>3.45</v>
       </c>
       <c r="W135">
@@ -13650,6 +13777,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V136">
+        <f>Y136/100</f>
         <v>3.45</v>
       </c>
       <c r="W136">
@@ -13748,6 +13876,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V137">
+        <f>Y137/100</f>
         <v>3.45</v>
       </c>
       <c r="W137">
@@ -13846,6 +13975,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V138">
+        <f>Y138/100</f>
         <v>3.45</v>
       </c>
       <c r="W138">
@@ -13944,6 +14074,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V139">
+        <f>Y139/100</f>
         <v>3.45</v>
       </c>
       <c r="W139">
@@ -14042,6 +14173,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V140">
+        <f>Y140/100</f>
         <v>3.45</v>
       </c>
       <c r="W140">
@@ -14140,6 +14272,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V141">
+        <f>Y141/100</f>
         <v>3.45</v>
       </c>
       <c r="W141">
@@ -14238,6 +14371,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V142">
+        <f>Y142/100</f>
         <v>3.45</v>
       </c>
       <c r="W142">
@@ -14336,6 +14470,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V143">
+        <f>Y143/100</f>
         <v>3.45</v>
       </c>
       <c r="W143">
@@ -14434,6 +14569,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V144">
+        <f>Y144/100</f>
         <v>4.94</v>
       </c>
       <c r="W144">
@@ -14532,6 +14668,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V145">
+        <f>Y145/100</f>
         <v>3.8</v>
       </c>
       <c r="W145">
@@ -14630,6 +14767,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V146">
+        <f>Y146/100</f>
         <v>3.8</v>
       </c>
       <c r="W146">
@@ -14728,6 +14866,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V147">
+        <f>Y147/100</f>
         <v>3.8</v>
       </c>
       <c r="W147">
@@ -14826,6 +14965,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V148">
+        <f>Y148/100</f>
         <v>3.8</v>
       </c>
       <c r="W148">
@@ -14924,6 +15064,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V149">
+        <f>Y149/100</f>
         <v>3.8</v>
       </c>
       <c r="W149">
@@ -15022,6 +15163,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V150">
+        <f>Y150/100</f>
         <v>3.8</v>
       </c>
       <c r="W150">
@@ -15120,6 +15262,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V151">
+        <f>Y151/100</f>
         <v>3.8</v>
       </c>
       <c r="W151">
@@ -15218,6 +15361,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V152">
+        <f>Y152/100</f>
         <v>3.8</v>
       </c>
       <c r="W152">
@@ -15316,6 +15460,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V153">
+        <f>Y153/100</f>
         <v>3.8</v>
       </c>
       <c r="W153">
@@ -15414,6 +15559,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V154">
+        <f>Y154/100</f>
         <v>6.68</v>
       </c>
       <c r="W154">
@@ -15512,6 +15658,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V155">
+        <f>Y155/100</f>
         <v>4.18</v>
       </c>
       <c r="W155">
@@ -15610,6 +15757,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V156">
+        <f>Y156/100</f>
         <v>4.18</v>
       </c>
       <c r="W156">
@@ -15708,6 +15856,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V157">
+        <f>Y157/100</f>
         <v>4.18</v>
       </c>
       <c r="W157">
@@ -15806,6 +15955,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V158">
+        <f>Y158/100</f>
         <v>4.18</v>
       </c>
       <c r="W158">
@@ -15904,6 +16054,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V159">
+        <f>Y159/100</f>
         <v>4.18</v>
       </c>
       <c r="W159">
@@ -16002,6 +16153,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V160">
+        <f>Y160/100</f>
         <v>4.18</v>
       </c>
       <c r="W160">
@@ -16100,6 +16252,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V161">
+        <f>Y161/100</f>
         <v>4.18</v>
       </c>
       <c r="W161">
@@ -16198,6 +16351,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V162">
+        <f>Y162/100</f>
         <v>4.18</v>
       </c>
       <c r="W162">
@@ -16296,6 +16450,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V163">
+        <f>Y163/100</f>
         <v>4.18</v>
       </c>
       <c r="W163">
@@ -16394,6 +16549,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V164">
+        <f>Y164/100</f>
         <v>5.97</v>
       </c>
       <c r="W164">
@@ -16492,6 +16648,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V165">
+        <f>Y165/100</f>
         <v>4.59</v>
       </c>
       <c r="W165">
@@ -16590,6 +16747,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V166">
+        <f>Y166/100</f>
         <v>4.59</v>
       </c>
       <c r="W166">
@@ -16688,6 +16846,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V167">
+        <f>Y167/100</f>
         <v>4.59</v>
       </c>
       <c r="W167">
@@ -16786,6 +16945,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V168">
+        <f>Y168/100</f>
         <v>4.59</v>
       </c>
       <c r="W168">
@@ -16884,6 +17044,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V169">
+        <f>Y169/100</f>
         <v>4.59</v>
       </c>
       <c r="W169">
@@ -16982,6 +17143,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V170">
+        <f>Y170/100</f>
         <v>4.59</v>
       </c>
       <c r="W170">
@@ -17080,6 +17242,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V171">
+        <f>Y171/100</f>
         <v>4.59</v>
       </c>
       <c r="W171">
@@ -17178,6 +17341,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V172">
+        <f>Y172/100</f>
         <v>4.59</v>
       </c>
       <c r="W172">
@@ -17276,6 +17440,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V173">
+        <f>Y173/100</f>
         <v>4.59</v>
       </c>
       <c r="W173">
@@ -17374,6 +17539,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V174">
+        <f>Y174/100</f>
         <v>6.57</v>
       </c>
       <c r="W174">
@@ -17472,6 +17638,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V175">
+        <f>Y175/100</f>
         <v>5.05</v>
       </c>
       <c r="W175">
@@ -17570,6 +17737,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V176">
+        <f>Y176/100</f>
         <v>5.05</v>
       </c>
       <c r="W176">
@@ -17668,6 +17836,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V177">
+        <f>Y177/100</f>
         <v>5.05</v>
       </c>
       <c r="W177">
@@ -17766,6 +17935,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V178">
+        <f>Y178/100</f>
         <v>5.05</v>
       </c>
       <c r="W178">
@@ -17864,6 +18034,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V179">
+        <f>Y179/100</f>
         <v>5.05</v>
       </c>
       <c r="W179">
@@ -17962,6 +18133,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V180">
+        <f>Y180/100</f>
         <v>5.05</v>
       </c>
       <c r="W180">
@@ -18060,6 +18232,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V181">
+        <f>Y181/100</f>
         <v>5.05</v>
       </c>
       <c r="W181">
@@ -18158,6 +18331,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V182">
+        <f>Y182/100</f>
         <v>5.05</v>
       </c>
       <c r="W182">
@@ -18256,6 +18430,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V183">
+        <f>Y183/100</f>
         <v>5.05</v>
       </c>
       <c r="W183">
@@ -18354,6 +18529,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V184">
+        <f>Y184/100</f>
         <v>7.23</v>
       </c>
       <c r="W184">
@@ -18452,6 +18628,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V185">
+        <f>Y185/100</f>
         <v>5.56</v>
       </c>
       <c r="W185">
@@ -18550,6 +18727,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V186">
+        <f>Y186/100</f>
         <v>5.56</v>
       </c>
       <c r="W186">
@@ -18648,6 +18826,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V187">
+        <f>Y187/100</f>
         <v>5.56</v>
       </c>
       <c r="W187">
@@ -18746,6 +18925,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V188">
+        <f>Y188/100</f>
         <v>5.56</v>
       </c>
       <c r="W188">
@@ -18844,6 +19024,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V189">
+        <f>Y189/100</f>
         <v>5.56</v>
       </c>
       <c r="W189">
@@ -18942,6 +19123,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V190">
+        <f>Y190/100</f>
         <v>5.56</v>
       </c>
       <c r="W190">
@@ -19040,6 +19222,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V191">
+        <f>Y191/100</f>
         <v>5.56</v>
       </c>
       <c r="W191">
@@ -19138,6 +19321,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V192">
+        <f>Y192/100</f>
         <v>5.56</v>
       </c>
       <c r="W192">
@@ -19236,6 +19420,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V193">
+        <f>Y193/100</f>
         <v>5.56</v>
       </c>
       <c r="W193">
@@ -19334,6 +19519,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V194">
+        <f>Y194/100</f>
         <v>7.95</v>
       </c>
       <c r="W194">
@@ -19432,6 +19618,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V195">
+        <f>Y195/100</f>
         <v>6.12</v>
       </c>
       <c r="W195">
@@ -19530,6 +19717,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V196">
+        <f>Y196/100</f>
         <v>6.12</v>
       </c>
       <c r="W196">
@@ -19628,6 +19816,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V197">
+        <f>Y197/100</f>
         <v>6.12</v>
       </c>
       <c r="W197">
@@ -19726,6 +19915,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V198">
+        <f>Y198/100</f>
         <v>6.12</v>
       </c>
       <c r="W198">
@@ -19824,6 +20014,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V199">
+        <f>Y199/100</f>
         <v>6.12</v>
       </c>
       <c r="W199">
@@ -19922,6 +20113,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V200">
+        <f>Y200/100</f>
         <v>6.12</v>
       </c>
       <c r="W200">
@@ -20020,6 +20212,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V201">
+        <f>Y201/100</f>
         <v>6.12</v>
       </c>
       <c r="W201">
@@ -20118,6 +20311,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V202">
+        <f>Y202/100</f>
         <v>6.12</v>
       </c>
       <c r="W202">
@@ -20216,6 +20410,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V203">
+        <f>Y203/100</f>
         <v>6.12</v>
       </c>
       <c r="W203">
@@ -20314,6 +20509,7 @@
         <v>[[[]]]</v>
       </c>
       <c r="V204">
+        <f>Y204/100</f>
         <v>10.76</v>
       </c>
       <c r="W204">

--- a/public/StageTable.xlsx
+++ b/public/StageTable.xlsx
@@ -435,7 +435,7 @@
     <col min="34" max="34" customWidth="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="14.25" customHeight="1">
       <c r="A1" t="str">
         <v>#</v>
       </c>
@@ -443,7 +443,7 @@
         <v>关卡表</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="str">
         <v>#</v>
       </c>
@@ -544,7 +544,7 @@
         <v>StarGoal</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="str">
         <v>#</v>
       </c>
@@ -645,7 +645,7 @@
         <v>string</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="14.25" customHeight="1">
       <c r="A4" t="str">
         <v>#</v>
       </c>
@@ -746,7 +746,7 @@
         <v>星级挑战要求</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="14.25" customHeight="1">
       <c r="B5">
         <v>1</v>
       </c>
@@ -845,7 +845,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="14.25" customHeight="1">
       <c r="B6">
         <v>2</v>
       </c>
@@ -944,7 +944,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="14.25" customHeight="1">
       <c r="B7">
         <v>3</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="14.25" customHeight="1">
       <c r="B8">
         <v>4</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="14.25" customHeight="1">
       <c r="B9">
         <v>5</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="14.25" customHeight="1">
       <c r="B10">
         <v>6</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="14.25" customHeight="1">
       <c r="B11">
         <v>7</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="14.25" customHeight="1">
       <c r="B12">
         <v>8</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="14.25" customHeight="1">
       <c r="B13">
         <v>9</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="14.25" customHeight="1">
       <c r="B14">
         <v>10</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="14.25" customHeight="1">
       <c r="B15">
         <v>11</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="14.25" customHeight="1">
       <c r="B16">
         <v>12</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="14.25" customHeight="1">
       <c r="B17">
         <v>13</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="14.25" customHeight="1">
       <c r="B18">
         <v>14</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="14.25" customHeight="1">
       <c r="B19">
         <v>15</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="14.25" customHeight="1">
       <c r="B20">
         <v>16</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="14.25" customHeight="1">
       <c r="B21">
         <v>17</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="14.25" customHeight="1">
       <c r="B22">
         <v>18</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="14.25" customHeight="1">
       <c r="B23">
         <v>19</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="14.25" customHeight="1">
       <c r="B24">
         <v>20</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="14.25" customHeight="1">
       <c r="B25">
         <v>21</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="14.25" customHeight="1">
       <c r="B26">
         <v>22</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="14.25" customHeight="1">
       <c r="B27">
         <v>23</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="14.25" customHeight="1">
       <c r="B28">
         <v>24</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="14.25" customHeight="1">
       <c r="B29">
         <v>25</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="14.25" customHeight="1">
       <c r="B30">
         <v>26</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="14.25" customHeight="1">
       <c r="B31">
         <v>27</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="14.25" customHeight="1">
       <c r="B32">
         <v>28</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="14.25" customHeight="1">
       <c r="B33">
         <v>29</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="14.25" customHeight="1">
       <c r="B34">
         <v>30</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="14.25" customHeight="1">
       <c r="B35">
         <v>31</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="14.25" customHeight="1">
       <c r="B36">
         <v>32</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="14.25" customHeight="1">
       <c r="B37">
         <v>33</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="14.25" customHeight="1">
       <c r="B38">
         <v>34</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="14.25" customHeight="1">
       <c r="B39">
         <v>35</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="14.25" customHeight="1">
       <c r="B40">
         <v>36</v>
       </c>
@@ -4310,7 +4310,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="14.25" customHeight="1">
       <c r="B41">
         <v>37</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="14.25" customHeight="1">
       <c r="B42">
         <v>38</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="14.25" customHeight="1">
       <c r="B43">
         <v>39</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="14.25" customHeight="1">
       <c r="B44">
         <v>40</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="14.25" customHeight="1">
       <c r="B45">
         <v>41</v>
       </c>
@@ -4805,7 +4805,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="14.25" customHeight="1">
       <c r="B46">
         <v>42</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="14.25" customHeight="1">
       <c r="B47">
         <v>43</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="14.25" customHeight="1">
       <c r="B48">
         <v>44</v>
       </c>
@@ -5102,7 +5102,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="14.25" customHeight="1">
       <c r="B49">
         <v>45</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="14.25" customHeight="1">
       <c r="B50">
         <v>46</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="14.25" customHeight="1">
       <c r="B51">
         <v>47</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="14.25" customHeight="1">
       <c r="B52">
         <v>48</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="14.25" customHeight="1">
       <c r="B53">
         <v>49</v>
       </c>
@@ -5597,7 +5597,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="14.25" customHeight="1">
       <c r="B54">
         <v>50</v>
       </c>
@@ -5696,7 +5696,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="14.25" customHeight="1">
       <c r="B55">
         <v>51</v>
       </c>
@@ -5795,7 +5795,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="14.25" customHeight="1">
       <c r="B56">
         <v>52</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="14.25" customHeight="1">
       <c r="B57">
         <v>53</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="14.25" customHeight="1">
       <c r="B58">
         <v>54</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="14.25" customHeight="1">
       <c r="B59">
         <v>55</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="14.25" customHeight="1">
       <c r="B60">
         <v>56</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="14.25" customHeight="1">
       <c r="B61">
         <v>57</v>
       </c>
@@ -6389,7 +6389,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="14.25" customHeight="1">
       <c r="B62">
         <v>58</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="14.25" customHeight="1">
       <c r="B63">
         <v>59</v>
       </c>
@@ -6587,7 +6587,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="14.25" customHeight="1">
       <c r="B64">
         <v>60</v>
       </c>
@@ -6686,7 +6686,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="14.25" customHeight="1">
       <c r="B65">
         <v>61</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="14.25" customHeight="1">
       <c r="B66">
         <v>62</v>
       </c>
@@ -6884,7 +6884,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="14.25" customHeight="1">
       <c r="B67">
         <v>63</v>
       </c>
@@ -6983,7 +6983,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="14.25" customHeight="1">
       <c r="B68">
         <v>64</v>
       </c>
@@ -7082,7 +7082,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="14.25" customHeight="1">
       <c r="B69">
         <v>65</v>
       </c>
@@ -7181,7 +7181,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="14.25" customHeight="1">
       <c r="B70">
         <v>66</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="14.25" customHeight="1">
       <c r="B71">
         <v>67</v>
       </c>
@@ -7379,7 +7379,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="14.25" customHeight="1">
       <c r="B72">
         <v>68</v>
       </c>
@@ -7478,7 +7478,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="14.25" customHeight="1">
       <c r="B73">
         <v>69</v>
       </c>
@@ -7577,7 +7577,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="14.25" customHeight="1">
       <c r="B74">
         <v>70</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="14.25" customHeight="1">
       <c r="B75">
         <v>71</v>
       </c>
@@ -7775,7 +7775,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="14.25" customHeight="1">
       <c r="B76">
         <v>72</v>
       </c>
@@ -7874,7 +7874,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="14.25" customHeight="1">
       <c r="B77">
         <v>73</v>
       </c>
@@ -7973,7 +7973,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="14.25" customHeight="1">
       <c r="B78">
         <v>74</v>
       </c>
@@ -8072,7 +8072,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="14.25" customHeight="1">
       <c r="B79">
         <v>75</v>
       </c>
@@ -8171,7 +8171,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="14.25" customHeight="1">
       <c r="B80">
         <v>76</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="14.25" customHeight="1">
       <c r="B81">
         <v>77</v>
       </c>
@@ -8369,7 +8369,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="14.25" customHeight="1">
       <c r="B82">
         <v>78</v>
       </c>
@@ -8468,7 +8468,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="14.25" customHeight="1">
       <c r="B83">
         <v>79</v>
       </c>
@@ -8567,7 +8567,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="14.25" customHeight="1">
       <c r="B84">
         <v>80</v>
       </c>
@@ -8666,7 +8666,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="14.25" customHeight="1">
       <c r="B85">
         <v>81</v>
       </c>
@@ -8765,7 +8765,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="14.25" customHeight="1">
       <c r="B86">
         <v>82</v>
       </c>
@@ -8864,7 +8864,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="14.25" customHeight="1">
       <c r="B87">
         <v>83</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="14.25" customHeight="1">
       <c r="B88">
         <v>84</v>
       </c>
@@ -9062,7 +9062,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="14.25" customHeight="1">
       <c r="B89">
         <v>85</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="14.25" customHeight="1">
       <c r="B90">
         <v>86</v>
       </c>
@@ -9260,7 +9260,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="14.25" customHeight="1">
       <c r="B91">
         <v>87</v>
       </c>
@@ -9359,7 +9359,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="14.25" customHeight="1">
       <c r="B92">
         <v>88</v>
       </c>
@@ -9458,7 +9458,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="14.25" customHeight="1">
       <c r="B93">
         <v>89</v>
       </c>
@@ -9557,7 +9557,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="14.25" customHeight="1">
       <c r="B94">
         <v>90</v>
       </c>
@@ -9656,7 +9656,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="14.25" customHeight="1">
       <c r="B95">
         <v>91</v>
       </c>
@@ -9755,7 +9755,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="14.25" customHeight="1">
       <c r="B96">
         <v>92</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="14.25" customHeight="1">
       <c r="B97">
         <v>93</v>
       </c>
@@ -9953,7 +9953,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="14.25" customHeight="1">
       <c r="B98">
         <v>94</v>
       </c>
@@ -10052,7 +10052,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="14.25" customHeight="1">
       <c r="B99">
         <v>95</v>
       </c>
@@ -10151,7 +10151,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="14.25" customHeight="1">
       <c r="B100">
         <v>96</v>
       </c>
@@ -10250,7 +10250,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="14.25" customHeight="1">
       <c r="B101">
         <v>97</v>
       </c>
@@ -10349,7 +10349,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="14.25" customHeight="1">
       <c r="B102">
         <v>98</v>
       </c>
@@ -10448,7 +10448,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="14.25" customHeight="1">
       <c r="B103">
         <v>99</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="14.25" customHeight="1">
       <c r="B104">
         <v>100</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="14.25" customHeight="1">
       <c r="B105">
         <v>101</v>
       </c>
@@ -10745,7 +10745,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="14.25" customHeight="1">
       <c r="B106">
         <v>102</v>
       </c>
@@ -10844,7 +10844,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="14.25" customHeight="1">
       <c r="B107">
         <v>103</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="14.25" customHeight="1">
       <c r="B108">
         <v>104</v>
       </c>
@@ -11042,7 +11042,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="14.25" customHeight="1">
       <c r="B109">
         <v>105</v>
       </c>
@@ -11141,7 +11141,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="14.25" customHeight="1">
       <c r="B110">
         <v>106</v>
       </c>
@@ -11240,7 +11240,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="14.25" customHeight="1">
       <c r="B111">
         <v>107</v>
       </c>
@@ -11339,7 +11339,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="14.25" customHeight="1">
       <c r="B112">
         <v>108</v>
       </c>
@@ -11438,7 +11438,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="14.25" customHeight="1">
       <c r="B113">
         <v>109</v>
       </c>
@@ -11537,7 +11537,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="14.25" customHeight="1">
       <c r="B114">
         <v>110</v>
       </c>
@@ -11636,7 +11636,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="14.25" customHeight="1">
       <c r="B115">
         <v>111</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="14.25" customHeight="1">
       <c r="B116">
         <v>112</v>
       </c>
@@ -11834,7 +11834,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="14.25" customHeight="1">
       <c r="B117">
         <v>113</v>
       </c>
@@ -11933,7 +11933,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="14.25" customHeight="1">
       <c r="B118">
         <v>114</v>
       </c>
@@ -12032,7 +12032,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" ht="14.25" customHeight="1">
       <c r="B119">
         <v>115</v>
       </c>
@@ -12131,7 +12131,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="14.25" customHeight="1">
       <c r="B120">
         <v>116</v>
       </c>
@@ -12230,7 +12230,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="14.25" customHeight="1">
       <c r="B121">
         <v>117</v>
       </c>
@@ -12329,7 +12329,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="14.25" customHeight="1">
       <c r="B122">
         <v>118</v>
       </c>
@@ -12428,7 +12428,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="14.25" customHeight="1">
       <c r="B123">
         <v>119</v>
       </c>
@@ -12527,7 +12527,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="14.25" customHeight="1">
       <c r="B124">
         <v>120</v>
       </c>
@@ -12626,7 +12626,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="14.25" customHeight="1">
       <c r="B125">
         <v>121</v>
       </c>
@@ -12725,7 +12725,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="14.25" customHeight="1">
       <c r="B126">
         <v>122</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="14.25" customHeight="1">
       <c r="B127">
         <v>123</v>
       </c>
@@ -12923,7 +12923,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="14.25" customHeight="1">
       <c r="B128">
         <v>124</v>
       </c>
@@ -13022,7 +13022,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="14.25" customHeight="1">
       <c r="B129">
         <v>125</v>
       </c>
@@ -13121,7 +13121,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="14.25" customHeight="1">
       <c r="B130">
         <v>126</v>
       </c>
@@ -13220,7 +13220,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="14.25" customHeight="1">
       <c r="B131">
         <v>127</v>
       </c>
@@ -13319,7 +13319,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="14.25" customHeight="1">
       <c r="B132">
         <v>128</v>
       </c>
@@ -13418,7 +13418,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="14.25" customHeight="1">
       <c r="B133">
         <v>129</v>
       </c>
@@ -13517,7 +13517,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="14.25" customHeight="1">
       <c r="B134">
         <v>130</v>
       </c>
@@ -13616,7 +13616,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" ht="14.25" customHeight="1">
       <c r="B135">
         <v>131</v>
       </c>
@@ -13715,7 +13715,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="14.25" customHeight="1">
       <c r="B136">
         <v>132</v>
       </c>
@@ -13814,7 +13814,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" ht="14.25" customHeight="1">
       <c r="B137">
         <v>133</v>
       </c>
@@ -13913,7 +13913,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="14.25" customHeight="1">
       <c r="B138">
         <v>134</v>
       </c>
@@ -14012,7 +14012,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" ht="14.25" customHeight="1">
       <c r="B139">
         <v>135</v>
       </c>
@@ -14111,7 +14111,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" ht="14.25" customHeight="1">
       <c r="B140">
         <v>136</v>
       </c>
@@ -14210,7 +14210,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="14.25" customHeight="1">
       <c r="B141">
         <v>137</v>
       </c>
@@ -14309,7 +14309,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" ht="14.25" customHeight="1">
       <c r="B142">
         <v>138</v>
       </c>
@@ -14408,7 +14408,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" ht="14.25" customHeight="1">
       <c r="B143">
         <v>139</v>
       </c>
@@ -14507,7 +14507,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" ht="14.25" customHeight="1">
       <c r="B144">
         <v>140</v>
       </c>
@@ -14606,7 +14606,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" ht="14.25" customHeight="1">
       <c r="B145">
         <v>141</v>
       </c>
@@ -14705,7 +14705,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" ht="14.25" customHeight="1">
       <c r="B146">
         <v>142</v>
       </c>
@@ -14804,7 +14804,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" ht="14.25" customHeight="1">
       <c r="B147">
         <v>143</v>
       </c>
@@ -14903,7 +14903,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" ht="14.25" customHeight="1">
       <c r="B148">
         <v>144</v>
       </c>
@@ -15002,7 +15002,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" ht="14.25" customHeight="1">
       <c r="B149">
         <v>145</v>
       </c>
@@ -15101,7 +15101,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" ht="14.25" customHeight="1">
       <c r="B150">
         <v>146</v>
       </c>
@@ -15200,7 +15200,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" ht="14.25" customHeight="1">
       <c r="B151">
         <v>147</v>
       </c>
@@ -15299,7 +15299,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" ht="14.25" customHeight="1">
       <c r="B152">
         <v>148</v>
       </c>
@@ -15398,7 +15398,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" ht="14.25" customHeight="1">
       <c r="B153">
         <v>149</v>
       </c>
@@ -15497,7 +15497,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" ht="14.25" customHeight="1">
       <c r="B154">
         <v>150</v>
       </c>
@@ -15596,7 +15596,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" ht="14.25" customHeight="1">
       <c r="B155">
         <v>151</v>
       </c>
@@ -15695,7 +15695,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" ht="14.25" customHeight="1">
       <c r="B156">
         <v>152</v>
       </c>
@@ -15794,7 +15794,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" ht="14.25" customHeight="1">
       <c r="B157">
         <v>153</v>
       </c>
@@ -15893,7 +15893,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" ht="14.25" customHeight="1">
       <c r="B158">
         <v>154</v>
       </c>
@@ -15992,7 +15992,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" ht="14.25" customHeight="1">
       <c r="B159">
         <v>155</v>
       </c>
@@ -16091,7 +16091,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" ht="14.25" customHeight="1">
       <c r="B160">
         <v>156</v>
       </c>
@@ -16190,7 +16190,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" ht="14.25" customHeight="1">
       <c r="B161">
         <v>157</v>
       </c>
@@ -16289,7 +16289,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" ht="14.25" customHeight="1">
       <c r="B162">
         <v>158</v>
       </c>
@@ -16388,7 +16388,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" ht="14.25" customHeight="1">
       <c r="B163">
         <v>159</v>
       </c>
@@ -16487,7 +16487,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" ht="14.25" customHeight="1">
       <c r="B164">
         <v>160</v>
       </c>
@@ -16586,7 +16586,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" ht="14.25" customHeight="1">
       <c r="B165">
         <v>161</v>
       </c>
@@ -16685,7 +16685,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" ht="14.25" customHeight="1">
       <c r="B166">
         <v>162</v>
       </c>
@@ -16784,7 +16784,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" ht="14.25" customHeight="1">
       <c r="B167">
         <v>163</v>
       </c>
@@ -16883,7 +16883,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" ht="14.25" customHeight="1">
       <c r="B168">
         <v>164</v>
       </c>
@@ -16982,7 +16982,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" ht="14.25" customHeight="1">
       <c r="B169">
         <v>165</v>
       </c>
@@ -17081,7 +17081,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" ht="14.25" customHeight="1">
       <c r="B170">
         <v>166</v>
       </c>
@@ -17180,7 +17180,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" ht="14.25" customHeight="1">
       <c r="B171">
         <v>167</v>
       </c>
@@ -17279,7 +17279,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" ht="14.25" customHeight="1">
       <c r="B172">
         <v>168</v>
       </c>
@@ -17378,7 +17378,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" ht="14.25" customHeight="1">
       <c r="B173">
         <v>169</v>
       </c>
@@ -17477,7 +17477,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" ht="14.25" customHeight="1">
       <c r="B174">
         <v>170</v>
       </c>
@@ -17576,7 +17576,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" ht="14.25" customHeight="1">
       <c r="B175">
         <v>171</v>
       </c>
@@ -17675,7 +17675,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" ht="14.25" customHeight="1">
       <c r="B176">
         <v>172</v>
       </c>
@@ -17774,7 +17774,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" ht="14.25" customHeight="1">
       <c r="B177">
         <v>173</v>
       </c>
@@ -17873,7 +17873,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" ht="14.25" customHeight="1">
       <c r="B178">
         <v>174</v>
       </c>
@@ -17972,7 +17972,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" ht="14.25" customHeight="1">
       <c r="B179">
         <v>175</v>
       </c>
@@ -18071,7 +18071,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" ht="14.25" customHeight="1">
       <c r="B180">
         <v>176</v>
       </c>
@@ -18170,7 +18170,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" ht="14.25" customHeight="1">
       <c r="B181">
         <v>177</v>
       </c>
@@ -18269,7 +18269,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" ht="14.25" customHeight="1">
       <c r="B182">
         <v>178</v>
       </c>
@@ -18368,7 +18368,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" ht="14.25" customHeight="1">
       <c r="B183">
         <v>179</v>
       </c>
@@ -18467,7 +18467,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" ht="14.25" customHeight="1">
       <c r="B184">
         <v>180</v>
       </c>
@@ -18566,7 +18566,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" ht="14.25" customHeight="1">
       <c r="B185">
         <v>181</v>
       </c>
@@ -18665,7 +18665,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" ht="14.25" customHeight="1">
       <c r="B186">
         <v>182</v>
       </c>
@@ -18764,7 +18764,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" ht="14.25" customHeight="1">
       <c r="B187">
         <v>183</v>
       </c>
@@ -18863,7 +18863,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" ht="14.25" customHeight="1">
       <c r="B188">
         <v>184</v>
       </c>
@@ -18962,7 +18962,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" ht="14.25" customHeight="1">
       <c r="B189">
         <v>185</v>
       </c>
@@ -19061,7 +19061,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" ht="14.25" customHeight="1">
       <c r="B190">
         <v>186</v>
       </c>
@@ -19160,7 +19160,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" ht="14.25" customHeight="1">
       <c r="B191">
         <v>187</v>
       </c>
@@ -19259,7 +19259,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" ht="14.25" customHeight="1">
       <c r="B192">
         <v>188</v>
       </c>
@@ -19358,7 +19358,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" ht="14.25" customHeight="1">
       <c r="B193">
         <v>189</v>
       </c>
@@ -19457,7 +19457,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" ht="14.25" customHeight="1">
       <c r="B194">
         <v>190</v>
       </c>
@@ -19556,7 +19556,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" ht="14.25" customHeight="1">
       <c r="B195">
         <v>191</v>
       </c>
@@ -19655,7 +19655,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" ht="14.25" customHeight="1">
       <c r="B196">
         <v>192</v>
       </c>
@@ -19754,7 +19754,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" ht="14.25" customHeight="1">
       <c r="B197">
         <v>193</v>
       </c>
@@ -19853,7 +19853,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" ht="14.25" customHeight="1">
       <c r="B198">
         <v>194</v>
       </c>
@@ -19952,7 +19952,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" ht="14.25" customHeight="1">
       <c r="B199">
         <v>195</v>
       </c>
@@ -20051,7 +20051,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" ht="14.25" customHeight="1">
       <c r="B200">
         <v>196</v>
       </c>
@@ -20150,7 +20150,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" ht="14.25" customHeight="1">
       <c r="B201">
         <v>197</v>
       </c>
@@ -20249,7 +20249,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" ht="14.25" customHeight="1">
       <c r="B202">
         <v>198</v>
       </c>
@@ -20348,7 +20348,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" ht="14.25" customHeight="1">
       <c r="B203">
         <v>199</v>
       </c>
@@ -20447,7 +20447,7 @@
         <v>[240,0.9,6]</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" ht="14.25" customHeight="1">
       <c r="B204">
         <v>200</v>
       </c>

--- a/public/StageTable.xlsx
+++ b/public/StageTable.xlsx
@@ -32,7 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -809,10 +813,10 @@
       </c>
       <c r="V5">
         <f>Y5/100</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="W5">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="X5">
         <v>1</v>
@@ -908,10 +912,10 @@
       </c>
       <c r="V6">
         <f>Y6/100</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="X6">
         <v>1</v>
@@ -1007,10 +1011,10 @@
       </c>
       <c r="V7">
         <f>Y7/100</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="W7">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="X7">
         <v>1</v>
@@ -1106,10 +1110,10 @@
       </c>
       <c r="V8">
         <f>Y8/100</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="W8">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="X8">
         <v>1</v>
@@ -1205,10 +1209,10 @@
       </c>
       <c r="V9">
         <f>Y9/100</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="W9">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="X9">
         <v>1</v>
@@ -1304,10 +1308,10 @@
       </c>
       <c r="V10">
         <f>Y10/100</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="W10">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="X10">
         <v>1</v>
@@ -1403,10 +1407,10 @@
       </c>
       <c r="V11">
         <f>Y11/100</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="W11">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="X11">
         <v>1</v>
@@ -1502,10 +1506,10 @@
       </c>
       <c r="V12">
         <f>Y12/100</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="W12">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="X12">
         <v>1</v>
@@ -1601,10 +1605,10 @@
       </c>
       <c r="V13">
         <f>Y13/100</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="W13">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="X13">
         <v>1</v>
@@ -1700,10 +1704,10 @@
       </c>
       <c r="V14">
         <f>Y14/100</f>
-        <v>1.43</v>
+        <v>0.43</v>
       </c>
       <c r="W14">
-        <v>1.32</v>
+        <v>0.4</v>
       </c>
       <c r="X14">
         <v>1.32</v>
@@ -1799,10 +1803,10 @@
       </c>
       <c r="V15">
         <f>Y15/100</f>
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="W15">
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="X15">
         <v>1.1</v>
@@ -1898,10 +1902,10 @@
       </c>
       <c r="V16">
         <f>Y16/100</f>
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="X16">
         <v>1.1</v>
@@ -1997,10 +2001,10 @@
       </c>
       <c r="V17">
         <f>Y17/100</f>
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="X17">
         <v>1.1</v>
@@ -2096,10 +2100,10 @@
       </c>
       <c r="V18">
         <f>Y18/100</f>
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="X18">
         <v>1.1</v>
@@ -2195,10 +2199,10 @@
       </c>
       <c r="V19">
         <f>Y19/100</f>
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="X19">
         <v>1.1</v>
@@ -2294,10 +2298,10 @@
       </c>
       <c r="V20">
         <f>Y20/100</f>
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="X20">
         <v>1.1</v>
@@ -2393,10 +2397,10 @@
       </c>
       <c r="V21">
         <f>Y21/100</f>
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="W21">
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="X21">
         <v>1.1</v>
@@ -2492,10 +2496,10 @@
       </c>
       <c r="V22">
         <f>Y22/100</f>
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="X22">
         <v>1.1</v>
@@ -2591,10 +2595,10 @@
       </c>
       <c r="V23">
         <f>Y23/100</f>
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="X23">
         <v>1.1</v>
@@ -2690,10 +2694,10 @@
       </c>
       <c r="V24">
         <f>Y24/100</f>
-        <v>1.57</v>
+        <v>0.47</v>
       </c>
       <c r="W24">
-        <v>1.45</v>
+        <v>0.44</v>
       </c>
       <c r="X24">
         <v>1.45</v>
@@ -2789,10 +2793,10 @@
       </c>
       <c r="V25">
         <f>Y25/100</f>
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="W25">
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="X25">
         <v>1.21</v>
@@ -2888,10 +2892,10 @@
       </c>
       <c r="V26">
         <f>Y26/100</f>
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="W26">
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="X26">
         <v>1.21</v>
@@ -2987,10 +2991,10 @@
       </c>
       <c r="V27">
         <f>Y27/100</f>
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="W27">
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="X27">
         <v>1.21</v>
@@ -3086,10 +3090,10 @@
       </c>
       <c r="V28">
         <f>Y28/100</f>
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="W28">
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="X28">
         <v>1.21</v>
@@ -3185,10 +3189,10 @@
       </c>
       <c r="V29">
         <f>Y29/100</f>
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="W29">
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="X29">
         <v>1.21</v>
@@ -3284,10 +3288,10 @@
       </c>
       <c r="V30">
         <f>Y30/100</f>
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="W30">
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="X30">
         <v>1.21</v>
@@ -3383,10 +3387,10 @@
       </c>
       <c r="V31">
         <f>Y31/100</f>
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="W31">
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="X31">
         <v>1.21</v>
@@ -3482,10 +3486,10 @@
       </c>
       <c r="V32">
         <f>Y32/100</f>
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="W32">
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="X32">
         <v>1.21</v>
@@ -3581,10 +3585,10 @@
       </c>
       <c r="V33">
         <f>Y33/100</f>
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="W33">
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="X33">
         <v>1.21</v>
@@ -3680,10 +3684,10 @@
       </c>
       <c r="V34">
         <f>Y34/100</f>
-        <v>1.73</v>
+        <v>0.52</v>
       </c>
       <c r="W34">
-        <v>1.6</v>
+        <v>0.48</v>
       </c>
       <c r="X34">
         <v>1.6</v>
@@ -3779,10 +3783,10 @@
       </c>
       <c r="V35">
         <f>Y35/100</f>
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="W35">
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="X35">
         <v>1.33</v>
@@ -3878,10 +3882,10 @@
       </c>
       <c r="V36">
         <f>Y36/100</f>
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="W36">
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="X36">
         <v>1.33</v>
@@ -3977,10 +3981,10 @@
       </c>
       <c r="V37">
         <f>Y37/100</f>
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="W37">
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="X37">
         <v>1.33</v>
@@ -4076,10 +4080,10 @@
       </c>
       <c r="V38">
         <f>Y38/100</f>
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="W38">
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="X38">
         <v>1.33</v>
@@ -4175,10 +4179,10 @@
       </c>
       <c r="V39">
         <f>Y39/100</f>
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="W39">
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="X39">
         <v>1.33</v>
@@ -4274,10 +4278,10 @@
       </c>
       <c r="V40">
         <f>Y40/100</f>
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="W40">
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="X40">
         <v>1.33</v>
@@ -4373,10 +4377,10 @@
       </c>
       <c r="V41">
         <f>Y41/100</f>
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="W41">
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="X41">
         <v>1.33</v>
@@ -4472,10 +4476,10 @@
       </c>
       <c r="V42">
         <f>Y42/100</f>
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="W42">
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="X42">
         <v>1.33</v>
@@ -4571,10 +4575,10 @@
       </c>
       <c r="V43">
         <f>Y43/100</f>
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="W43">
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="X43">
         <v>1.33</v>
@@ -4670,10 +4674,10 @@
       </c>
       <c r="V44">
         <f>Y44/100</f>
-        <v>1.9</v>
+        <v>0.57</v>
       </c>
       <c r="W44">
-        <v>1.76</v>
+        <v>0.53</v>
       </c>
       <c r="X44">
         <v>1.76</v>
@@ -4769,10 +4773,10 @@
       </c>
       <c r="V45">
         <f>Y45/100</f>
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="W45">
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="X45">
         <v>1.46</v>
@@ -4868,10 +4872,10 @@
       </c>
       <c r="V46">
         <f>Y46/100</f>
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="W46">
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="X46">
         <v>1.46</v>
@@ -4967,10 +4971,10 @@
       </c>
       <c r="V47">
         <f>Y47/100</f>
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="W47">
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="X47">
         <v>1.46</v>
@@ -5066,10 +5070,10 @@
       </c>
       <c r="V48">
         <f>Y48/100</f>
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="W48">
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="X48">
         <v>1.46</v>
@@ -5165,10 +5169,10 @@
       </c>
       <c r="V49">
         <f>Y49/100</f>
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="W49">
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="X49">
         <v>1.46</v>
@@ -5264,10 +5268,10 @@
       </c>
       <c r="V50">
         <f>Y50/100</f>
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="W50">
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="X50">
         <v>1.46</v>
@@ -5363,10 +5367,10 @@
       </c>
       <c r="V51">
         <f>Y51/100</f>
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="W51">
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="X51">
         <v>1.46</v>
@@ -5462,10 +5466,10 @@
       </c>
       <c r="V52">
         <f>Y52/100</f>
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="W52">
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="X52">
         <v>1.46</v>
@@ -5561,10 +5565,10 @@
       </c>
       <c r="V53">
         <f>Y53/100</f>
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="W53">
-        <v>1.46</v>
+        <v>0.44</v>
       </c>
       <c r="X53">
         <v>1.46</v>
@@ -5660,10 +5664,10 @@
       </c>
       <c r="V54">
         <f>Y54/100</f>
-        <v>2.58</v>
+        <v>0.77</v>
       </c>
       <c r="W54">
-        <v>2.25</v>
+        <v>0.68</v>
       </c>
       <c r="X54">
         <v>2.25</v>
@@ -5759,10 +5763,10 @@
       </c>
       <c r="V55">
         <f>Y55/100</f>
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="W55">
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="X55">
         <v>1.61</v>
@@ -5858,10 +5862,10 @@
       </c>
       <c r="V56">
         <f>Y56/100</f>
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="W56">
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="X56">
         <v>1.61</v>
@@ -5957,10 +5961,10 @@
       </c>
       <c r="V57">
         <f>Y57/100</f>
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="W57">
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="X57">
         <v>1.61</v>
@@ -6056,10 +6060,10 @@
       </c>
       <c r="V58">
         <f>Y58/100</f>
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="W58">
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="X58">
         <v>1.61</v>
@@ -6155,10 +6159,10 @@
       </c>
       <c r="V59">
         <f>Y59/100</f>
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="W59">
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="X59">
         <v>1.61</v>
@@ -6254,10 +6258,10 @@
       </c>
       <c r="V60">
         <f>Y60/100</f>
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="W60">
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="X60">
         <v>1.61</v>
@@ -6353,10 +6357,10 @@
       </c>
       <c r="V61">
         <f>Y61/100</f>
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="W61">
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="X61">
         <v>1.61</v>
@@ -6452,10 +6456,10 @@
       </c>
       <c r="V62">
         <f>Y62/100</f>
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="W62">
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="X62">
         <v>1.61</v>
@@ -6551,10 +6555,10 @@
       </c>
       <c r="V63">
         <f>Y63/100</f>
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="W63">
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="X63">
         <v>1.61</v>
@@ -6650,10 +6654,10 @@
       </c>
       <c r="V64">
         <f>Y64/100</f>
-        <v>2.3</v>
+        <v>0.69</v>
       </c>
       <c r="W64">
-        <v>2.13</v>
+        <v>0.64</v>
       </c>
       <c r="X64">
         <v>2.13</v>
@@ -6749,10 +6753,10 @@
       </c>
       <c r="V65">
         <f>Y65/100</f>
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="W65">
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="X65">
         <v>1.77</v>
@@ -6848,10 +6852,10 @@
       </c>
       <c r="V66">
         <f>Y66/100</f>
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="W66">
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="X66">
         <v>1.77</v>
@@ -6947,10 +6951,10 @@
       </c>
       <c r="V67">
         <f>Y67/100</f>
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="W67">
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="X67">
         <v>1.77</v>
@@ -7046,10 +7050,10 @@
       </c>
       <c r="V68">
         <f>Y68/100</f>
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="W68">
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="X68">
         <v>1.77</v>
@@ -7145,10 +7149,10 @@
       </c>
       <c r="V69">
         <f>Y69/100</f>
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="W69">
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="X69">
         <v>1.77</v>
@@ -7244,10 +7248,10 @@
       </c>
       <c r="V70">
         <f>Y70/100</f>
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="W70">
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="X70">
         <v>1.77</v>
@@ -7343,10 +7347,10 @@
       </c>
       <c r="V71">
         <f>Y71/100</f>
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="W71">
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="X71">
         <v>1.77</v>
@@ -7442,10 +7446,10 @@
       </c>
       <c r="V72">
         <f>Y72/100</f>
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="W72">
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="X72">
         <v>1.77</v>
@@ -7541,10 +7545,10 @@
       </c>
       <c r="V73">
         <f>Y73/100</f>
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="W73">
-        <v>1.77</v>
+        <v>0.53</v>
       </c>
       <c r="X73">
         <v>1.77</v>
@@ -7640,10 +7644,10 @@
       </c>
       <c r="V74">
         <f>Y74/100</f>
-        <v>2.53</v>
+        <v>0.76</v>
       </c>
       <c r="W74">
-        <v>2.34</v>
+        <v>0.7</v>
       </c>
       <c r="X74">
         <v>2.34</v>
@@ -7739,10 +7743,10 @@
       </c>
       <c r="V75">
         <f>Y75/100</f>
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="W75">
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="X75">
         <v>1.95</v>
@@ -7838,10 +7842,10 @@
       </c>
       <c r="V76">
         <f>Y76/100</f>
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="W76">
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="X76">
         <v>1.95</v>
@@ -7937,10 +7941,10 @@
       </c>
       <c r="V77">
         <f>Y77/100</f>
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="W77">
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="X77">
         <v>1.95</v>
@@ -8036,10 +8040,10 @@
       </c>
       <c r="V78">
         <f>Y78/100</f>
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="W78">
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="X78">
         <v>1.95</v>
@@ -8135,10 +8139,10 @@
       </c>
       <c r="V79">
         <f>Y79/100</f>
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="W79">
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="X79">
         <v>1.95</v>
@@ -8234,10 +8238,10 @@
       </c>
       <c r="V80">
         <f>Y80/100</f>
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="W80">
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="X80">
         <v>1.95</v>
@@ -8333,10 +8337,10 @@
       </c>
       <c r="V81">
         <f>Y81/100</f>
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="W81">
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="X81">
         <v>1.95</v>
@@ -8432,10 +8436,10 @@
       </c>
       <c r="V82">
         <f>Y82/100</f>
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="W82">
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="X82">
         <v>1.95</v>
@@ -8531,10 +8535,10 @@
       </c>
       <c r="V83">
         <f>Y83/100</f>
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="W83">
-        <v>1.95</v>
+        <v>0.58</v>
       </c>
       <c r="X83">
         <v>1.95</v>
@@ -8630,10 +8634,10 @@
       </c>
       <c r="V84">
         <f>Y84/100</f>
-        <v>2.79</v>
+        <v>0.84</v>
       </c>
       <c r="W84">
-        <v>2.57</v>
+        <v>0.77</v>
       </c>
       <c r="X84">
         <v>2.57</v>
@@ -8729,10 +8733,10 @@
       </c>
       <c r="V85">
         <f>Y85/100</f>
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="W85">
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="X85">
         <v>2.14</v>
@@ -8828,10 +8832,10 @@
       </c>
       <c r="V86">
         <f>Y86/100</f>
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="W86">
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="X86">
         <v>2.14</v>
@@ -8927,10 +8931,10 @@
       </c>
       <c r="V87">
         <f>Y87/100</f>
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="W87">
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="X87">
         <v>2.14</v>
@@ -9026,10 +9030,10 @@
       </c>
       <c r="V88">
         <f>Y88/100</f>
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="W88">
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="X88">
         <v>2.14</v>
@@ -9125,10 +9129,10 @@
       </c>
       <c r="V89">
         <f>Y89/100</f>
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="W89">
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="X89">
         <v>2.14</v>
@@ -9224,10 +9228,10 @@
       </c>
       <c r="V90">
         <f>Y90/100</f>
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="W90">
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="X90">
         <v>2.14</v>
@@ -9323,10 +9327,10 @@
       </c>
       <c r="V91">
         <f>Y91/100</f>
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="W91">
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="X91">
         <v>2.14</v>
@@ -9422,10 +9426,10 @@
       </c>
       <c r="V92">
         <f>Y92/100</f>
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="W92">
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="X92">
         <v>2.14</v>
@@ -9521,10 +9525,10 @@
       </c>
       <c r="V93">
         <f>Y93/100</f>
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="W93">
-        <v>2.14</v>
+        <v>0.64</v>
       </c>
       <c r="X93">
         <v>2.14</v>
@@ -9620,10 +9624,10 @@
       </c>
       <c r="V94">
         <f>Y94/100</f>
-        <v>3.07</v>
+        <v>0.92</v>
       </c>
       <c r="W94">
-        <v>2.83</v>
+        <v>0.85</v>
       </c>
       <c r="X94">
         <v>2.83</v>
@@ -9719,10 +9723,10 @@
       </c>
       <c r="V95">
         <f>Y95/100</f>
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="W95">
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="X95">
         <v>2.36</v>
@@ -9818,10 +9822,10 @@
       </c>
       <c r="V96">
         <f>Y96/100</f>
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="W96">
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="X96">
         <v>2.36</v>
@@ -9917,10 +9921,10 @@
       </c>
       <c r="V97">
         <f>Y97/100</f>
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="W97">
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="X97">
         <v>2.36</v>
@@ -10016,10 +10020,10 @@
       </c>
       <c r="V98">
         <f>Y98/100</f>
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="W98">
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="X98">
         <v>2.36</v>
@@ -10115,10 +10119,10 @@
       </c>
       <c r="V99">
         <f>Y99/100</f>
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="W99">
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="X99">
         <v>2.36</v>
@@ -10214,10 +10218,10 @@
       </c>
       <c r="V100">
         <f>Y100/100</f>
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="W100">
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="X100">
         <v>2.36</v>
@@ -10313,10 +10317,10 @@
       </c>
       <c r="V101">
         <f>Y101/100</f>
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="W101">
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="X101">
         <v>2.36</v>
@@ -10412,10 +10416,10 @@
       </c>
       <c r="V102">
         <f>Y102/100</f>
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="W102">
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="X102">
         <v>2.36</v>
@@ -10511,10 +10515,10 @@
       </c>
       <c r="V103">
         <f>Y103/100</f>
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="W103">
-        <v>2.36</v>
+        <v>0.71</v>
       </c>
       <c r="X103">
         <v>2.36</v>
@@ -10610,10 +10614,10 @@
       </c>
       <c r="V104">
         <f>Y104/100</f>
-        <v>4.15</v>
+        <v>1.24</v>
       </c>
       <c r="W104">
-        <v>3.63</v>
+        <v>1.09</v>
       </c>
       <c r="X104">
         <v>3.63</v>
@@ -10709,10 +10713,10 @@
       </c>
       <c r="V105">
         <f>Y105/100</f>
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="W105">
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="X105">
         <v>2.59</v>
@@ -10808,10 +10812,10 @@
       </c>
       <c r="V106">
         <f>Y106/100</f>
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="W106">
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="X106">
         <v>2.59</v>
@@ -10907,10 +10911,10 @@
       </c>
       <c r="V107">
         <f>Y107/100</f>
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="W107">
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="X107">
         <v>2.59</v>
@@ -11006,10 +11010,10 @@
       </c>
       <c r="V108">
         <f>Y108/100</f>
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="W108">
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="X108">
         <v>2.59</v>
@@ -11105,10 +11109,10 @@
       </c>
       <c r="V109">
         <f>Y109/100</f>
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="W109">
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="X109">
         <v>2.59</v>
@@ -11204,10 +11208,10 @@
       </c>
       <c r="V110">
         <f>Y110/100</f>
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="W110">
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="X110">
         <v>2.59</v>
@@ -11303,10 +11307,10 @@
       </c>
       <c r="V111">
         <f>Y111/100</f>
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="W111">
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="X111">
         <v>2.59</v>
@@ -11402,10 +11406,10 @@
       </c>
       <c r="V112">
         <f>Y112/100</f>
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="W112">
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="X112">
         <v>2.59</v>
@@ -11501,10 +11505,10 @@
       </c>
       <c r="V113">
         <f>Y113/100</f>
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="W113">
-        <v>2.59</v>
+        <v>0.78</v>
       </c>
       <c r="X113">
         <v>2.59</v>
@@ -11600,10 +11604,10 @@
       </c>
       <c r="V114">
         <f>Y114/100</f>
-        <v>3.71</v>
+        <v>1.11</v>
       </c>
       <c r="W114">
-        <v>3.42</v>
+        <v>1.03</v>
       </c>
       <c r="X114">
         <v>3.42</v>
@@ -11699,10 +11703,10 @@
       </c>
       <c r="V115">
         <f>Y115/100</f>
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="W115">
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="X115">
         <v>2.85</v>
@@ -11798,10 +11802,10 @@
       </c>
       <c r="V116">
         <f>Y116/100</f>
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="W116">
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="X116">
         <v>2.85</v>
@@ -11897,10 +11901,10 @@
       </c>
       <c r="V117">
         <f>Y117/100</f>
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="W117">
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="X117">
         <v>2.85</v>
@@ -11996,10 +12000,10 @@
       </c>
       <c r="V118">
         <f>Y118/100</f>
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="W118">
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="X118">
         <v>2.85</v>
@@ -12095,10 +12099,10 @@
       </c>
       <c r="V119">
         <f>Y119/100</f>
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="W119">
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="X119">
         <v>2.85</v>
@@ -12194,10 +12198,10 @@
       </c>
       <c r="V120">
         <f>Y120/100</f>
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="W120">
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="X120">
         <v>2.85</v>
@@ -12293,10 +12297,10 @@
       </c>
       <c r="V121">
         <f>Y121/100</f>
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="W121">
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="X121">
         <v>2.85</v>
@@ -12392,10 +12396,10 @@
       </c>
       <c r="V122">
         <f>Y122/100</f>
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="W122">
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="X122">
         <v>2.85</v>
@@ -12491,10 +12495,10 @@
       </c>
       <c r="V123">
         <f>Y123/100</f>
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="W123">
-        <v>2.85</v>
+        <v>0.86</v>
       </c>
       <c r="X123">
         <v>2.85</v>
@@ -12590,10 +12594,10 @@
       </c>
       <c r="V124">
         <f>Y124/100</f>
-        <v>4.08</v>
+        <v>1.22</v>
       </c>
       <c r="W124">
-        <v>3.77</v>
+        <v>1.13</v>
       </c>
       <c r="X124">
         <v>3.77</v>
@@ -12689,10 +12693,10 @@
       </c>
       <c r="V125">
         <f>Y125/100</f>
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="W125">
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="X125">
         <v>3.14</v>
@@ -12788,10 +12792,10 @@
       </c>
       <c r="V126">
         <f>Y126/100</f>
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="W126">
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="X126">
         <v>3.14</v>
@@ -12887,10 +12891,10 @@
       </c>
       <c r="V127">
         <f>Y127/100</f>
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="W127">
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="X127">
         <v>3.14</v>
@@ -12986,10 +12990,10 @@
       </c>
       <c r="V128">
         <f>Y128/100</f>
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="W128">
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="X128">
         <v>3.14</v>
@@ -13085,10 +13089,10 @@
       </c>
       <c r="V129">
         <f>Y129/100</f>
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="W129">
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="X129">
         <v>3.14</v>
@@ -13184,10 +13188,10 @@
       </c>
       <c r="V130">
         <f>Y130/100</f>
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="W130">
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="X130">
         <v>3.14</v>
@@ -13283,10 +13287,10 @@
       </c>
       <c r="V131">
         <f>Y131/100</f>
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="W131">
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="X131">
         <v>3.14</v>
@@ -13382,10 +13386,10 @@
       </c>
       <c r="V132">
         <f>Y132/100</f>
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="W132">
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="X132">
         <v>3.14</v>
@@ -13481,10 +13485,10 @@
       </c>
       <c r="V133">
         <f>Y133/100</f>
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="W133">
-        <v>3.14</v>
+        <v>0.94</v>
       </c>
       <c r="X133">
         <v>3.14</v>
@@ -13580,10 +13584,10 @@
       </c>
       <c r="V134">
         <f>Y134/100</f>
-        <v>4.49</v>
+        <v>1.35</v>
       </c>
       <c r="W134">
-        <v>4.14</v>
+        <v>1.24</v>
       </c>
       <c r="X134">
         <v>4.14</v>
@@ -13679,10 +13683,10 @@
       </c>
       <c r="V135">
         <f>Y135/100</f>
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="W135">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="X135">
         <v>3.45</v>
@@ -13778,10 +13782,10 @@
       </c>
       <c r="V136">
         <f>Y136/100</f>
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="W136">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="X136">
         <v>3.45</v>
@@ -13877,10 +13881,10 @@
       </c>
       <c r="V137">
         <f>Y137/100</f>
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="W137">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="X137">
         <v>3.45</v>
@@ -13976,10 +13980,10 @@
       </c>
       <c r="V138">
         <f>Y138/100</f>
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="W138">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="X138">
         <v>3.45</v>
@@ -14075,10 +14079,10 @@
       </c>
       <c r="V139">
         <f>Y139/100</f>
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="W139">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="X139">
         <v>3.45</v>
@@ -14174,10 +14178,10 @@
       </c>
       <c r="V140">
         <f>Y140/100</f>
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="W140">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="X140">
         <v>3.45</v>
@@ -14273,10 +14277,10 @@
       </c>
       <c r="V141">
         <f>Y141/100</f>
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="W141">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="X141">
         <v>3.45</v>
@@ -14372,10 +14376,10 @@
       </c>
       <c r="V142">
         <f>Y142/100</f>
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="W142">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="X142">
         <v>3.45</v>
@@ -14471,10 +14475,10 @@
       </c>
       <c r="V143">
         <f>Y143/100</f>
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="W143">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="X143">
         <v>3.45</v>
@@ -14570,10 +14574,10 @@
       </c>
       <c r="V144">
         <f>Y144/100</f>
-        <v>4.94</v>
+        <v>1.48</v>
       </c>
       <c r="W144">
-        <v>4.56</v>
+        <v>1.37</v>
       </c>
       <c r="X144">
         <v>4.56</v>
@@ -14669,10 +14673,10 @@
       </c>
       <c r="V145">
         <f>Y145/100</f>
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="W145">
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="X145">
         <v>3.8</v>
@@ -14768,10 +14772,10 @@
       </c>
       <c r="V146">
         <f>Y146/100</f>
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="W146">
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="X146">
         <v>3.8</v>
@@ -14867,10 +14871,10 @@
       </c>
       <c r="V147">
         <f>Y147/100</f>
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="W147">
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="X147">
         <v>3.8</v>
@@ -14966,10 +14970,10 @@
       </c>
       <c r="V148">
         <f>Y148/100</f>
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="W148">
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="X148">
         <v>3.8</v>
@@ -15065,10 +15069,10 @@
       </c>
       <c r="V149">
         <f>Y149/100</f>
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="W149">
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="X149">
         <v>3.8</v>
@@ -15164,10 +15168,10 @@
       </c>
       <c r="V150">
         <f>Y150/100</f>
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="W150">
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="X150">
         <v>3.8</v>
@@ -15263,10 +15267,10 @@
       </c>
       <c r="V151">
         <f>Y151/100</f>
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="W151">
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="X151">
         <v>3.8</v>
@@ -15362,10 +15366,10 @@
       </c>
       <c r="V152">
         <f>Y152/100</f>
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="W152">
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="X152">
         <v>3.8</v>
@@ -15461,10 +15465,10 @@
       </c>
       <c r="V153">
         <f>Y153/100</f>
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="W153">
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="X153">
         <v>3.8</v>
@@ -15560,10 +15564,10 @@
       </c>
       <c r="V154">
         <f>Y154/100</f>
-        <v>6.68</v>
+        <v>2.01</v>
       </c>
       <c r="W154">
-        <v>5.85</v>
+        <v>1.75</v>
       </c>
       <c r="X154">
         <v>5.85</v>
@@ -15659,10 +15663,10 @@
       </c>
       <c r="V155">
         <f>Y155/100</f>
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="W155">
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="X155">
         <v>4.18</v>
@@ -15758,10 +15762,10 @@
       </c>
       <c r="V156">
         <f>Y156/100</f>
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="W156">
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="X156">
         <v>4.18</v>
@@ -15857,10 +15861,10 @@
       </c>
       <c r="V157">
         <f>Y157/100</f>
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="W157">
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="X157">
         <v>4.18</v>
@@ -15956,10 +15960,10 @@
       </c>
       <c r="V158">
         <f>Y158/100</f>
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="W158">
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="X158">
         <v>4.18</v>
@@ -16055,10 +16059,10 @@
       </c>
       <c r="V159">
         <f>Y159/100</f>
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="W159">
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="X159">
         <v>4.18</v>
@@ -16154,10 +16158,10 @@
       </c>
       <c r="V160">
         <f>Y160/100</f>
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="W160">
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="X160">
         <v>4.18</v>
@@ -16253,10 +16257,10 @@
       </c>
       <c r="V161">
         <f>Y161/100</f>
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="W161">
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="X161">
         <v>4.18</v>
@@ -16352,10 +16356,10 @@
       </c>
       <c r="V162">
         <f>Y162/100</f>
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="W162">
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="X162">
         <v>4.18</v>
@@ -16451,10 +16455,10 @@
       </c>
       <c r="V163">
         <f>Y163/100</f>
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="W163">
-        <v>4.18</v>
+        <v>1.25</v>
       </c>
       <c r="X163">
         <v>4.18</v>
@@ -16550,10 +16554,10 @@
       </c>
       <c r="V164">
         <f>Y164/100</f>
-        <v>5.97</v>
+        <v>1.79</v>
       </c>
       <c r="W164">
-        <v>5.51</v>
+        <v>1.65</v>
       </c>
       <c r="X164">
         <v>5.51</v>
@@ -16649,10 +16653,10 @@
       </c>
       <c r="V165">
         <f>Y165/100</f>
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="W165">
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="X165">
         <v>4.59</v>
@@ -16748,10 +16752,10 @@
       </c>
       <c r="V166">
         <f>Y166/100</f>
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="W166">
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="X166">
         <v>4.59</v>
@@ -16847,10 +16851,10 @@
       </c>
       <c r="V167">
         <f>Y167/100</f>
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="W167">
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="X167">
         <v>4.59</v>
@@ -16946,10 +16950,10 @@
       </c>
       <c r="V168">
         <f>Y168/100</f>
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="W168">
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="X168">
         <v>4.59</v>
@@ -17045,10 +17049,10 @@
       </c>
       <c r="V169">
         <f>Y169/100</f>
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="W169">
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="X169">
         <v>4.59</v>
@@ -17144,10 +17148,10 @@
       </c>
       <c r="V170">
         <f>Y170/100</f>
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="W170">
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="X170">
         <v>4.59</v>
@@ -17243,10 +17247,10 @@
       </c>
       <c r="V171">
         <f>Y171/100</f>
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="W171">
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="X171">
         <v>4.59</v>
@@ -17342,10 +17346,10 @@
       </c>
       <c r="V172">
         <f>Y172/100</f>
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="W172">
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="X172">
         <v>4.59</v>
@@ -17441,10 +17445,10 @@
       </c>
       <c r="V173">
         <f>Y173/100</f>
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="W173">
-        <v>4.59</v>
+        <v>1.38</v>
       </c>
       <c r="X173">
         <v>4.59</v>
@@ -17540,10 +17544,10 @@
       </c>
       <c r="V174">
         <f>Y174/100</f>
-        <v>6.57</v>
+        <v>1.97</v>
       </c>
       <c r="W174">
-        <v>6.07</v>
+        <v>1.82</v>
       </c>
       <c r="X174">
         <v>6.07</v>
@@ -17639,10 +17643,10 @@
       </c>
       <c r="V175">
         <f>Y175/100</f>
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="W175">
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="X175">
         <v>5.05</v>
@@ -17738,10 +17742,10 @@
       </c>
       <c r="V176">
         <f>Y176/100</f>
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="W176">
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="X176">
         <v>5.05</v>
@@ -17837,10 +17841,10 @@
       </c>
       <c r="V177">
         <f>Y177/100</f>
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="W177">
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="X177">
         <v>5.05</v>
@@ -17936,10 +17940,10 @@
       </c>
       <c r="V178">
         <f>Y178/100</f>
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="W178">
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="X178">
         <v>5.05</v>
@@ -18035,10 +18039,10 @@
       </c>
       <c r="V179">
         <f>Y179/100</f>
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="W179">
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="X179">
         <v>5.05</v>
@@ -18134,10 +18138,10 @@
       </c>
       <c r="V180">
         <f>Y180/100</f>
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="W180">
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="X180">
         <v>5.05</v>
@@ -18233,10 +18237,10 @@
       </c>
       <c r="V181">
         <f>Y181/100</f>
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="W181">
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="X181">
         <v>5.05</v>
@@ -18332,10 +18336,10 @@
       </c>
       <c r="V182">
         <f>Y182/100</f>
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="W182">
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="X182">
         <v>5.05</v>
@@ -18431,10 +18435,10 @@
       </c>
       <c r="V183">
         <f>Y183/100</f>
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="W183">
-        <v>5.05</v>
+        <v>1.52</v>
       </c>
       <c r="X183">
         <v>5.05</v>
@@ -18530,10 +18534,10 @@
       </c>
       <c r="V184">
         <f>Y184/100</f>
-        <v>7.23</v>
+        <v>2.17</v>
       </c>
       <c r="W184">
-        <v>6.67</v>
+        <v>2</v>
       </c>
       <c r="X184">
         <v>6.67</v>
@@ -18629,10 +18633,10 @@
       </c>
       <c r="V185">
         <f>Y185/100</f>
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="W185">
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="X185">
         <v>5.56</v>
@@ -18728,10 +18732,10 @@
       </c>
       <c r="V186">
         <f>Y186/100</f>
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="W186">
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="X186">
         <v>5.56</v>
@@ -18827,10 +18831,10 @@
       </c>
       <c r="V187">
         <f>Y187/100</f>
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="W187">
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="X187">
         <v>5.56</v>
@@ -18926,10 +18930,10 @@
       </c>
       <c r="V188">
         <f>Y188/100</f>
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="W188">
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="X188">
         <v>5.56</v>
@@ -19025,10 +19029,10 @@
       </c>
       <c r="V189">
         <f>Y189/100</f>
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="W189">
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="X189">
         <v>5.56</v>
@@ -19124,10 +19128,10 @@
       </c>
       <c r="V190">
         <f>Y190/100</f>
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="W190">
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="X190">
         <v>5.56</v>
@@ -19223,10 +19227,10 @@
       </c>
       <c r="V191">
         <f>Y191/100</f>
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="W191">
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="X191">
         <v>5.56</v>
@@ -19322,10 +19326,10 @@
       </c>
       <c r="V192">
         <f>Y192/100</f>
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="W192">
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="X192">
         <v>5.56</v>
@@ -19421,10 +19425,10 @@
       </c>
       <c r="V193">
         <f>Y193/100</f>
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="W193">
-        <v>5.56</v>
+        <v>1.67</v>
       </c>
       <c r="X193">
         <v>5.56</v>
@@ -19520,10 +19524,10 @@
       </c>
       <c r="V194">
         <f>Y194/100</f>
-        <v>7.95</v>
+        <v>2.39</v>
       </c>
       <c r="W194">
-        <v>7.34</v>
+        <v>2.2</v>
       </c>
       <c r="X194">
         <v>7.34</v>
@@ -19619,10 +19623,10 @@
       </c>
       <c r="V195">
         <f>Y195/100</f>
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="W195">
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="X195">
         <v>6.12</v>
@@ -19718,10 +19722,10 @@
       </c>
       <c r="V196">
         <f>Y196/100</f>
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="W196">
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="X196">
         <v>6.12</v>
@@ -19817,10 +19821,10 @@
       </c>
       <c r="V197">
         <f>Y197/100</f>
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="W197">
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="X197">
         <v>6.12</v>
@@ -19916,10 +19920,10 @@
       </c>
       <c r="V198">
         <f>Y198/100</f>
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="W198">
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="X198">
         <v>6.12</v>
@@ -20015,10 +20019,10 @@
       </c>
       <c r="V199">
         <f>Y199/100</f>
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="W199">
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="X199">
         <v>6.12</v>
@@ -20114,10 +20118,10 @@
       </c>
       <c r="V200">
         <f>Y200/100</f>
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="W200">
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="X200">
         <v>6.12</v>
@@ -20213,10 +20217,10 @@
       </c>
       <c r="V201">
         <f>Y201/100</f>
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="W201">
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="X201">
         <v>6.12</v>
@@ -20312,10 +20316,10 @@
       </c>
       <c r="V202">
         <f>Y202/100</f>
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="W202">
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="X202">
         <v>6.12</v>
@@ -20411,10 +20415,10 @@
       </c>
       <c r="V203">
         <f>Y203/100</f>
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="W203">
-        <v>6.12</v>
+        <v>1.83</v>
       </c>
       <c r="X203">
         <v>6.12</v>
@@ -20510,10 +20514,10 @@
       </c>
       <c r="V204">
         <f>Y204/100</f>
-        <v>10.76</v>
+        <v>3.23</v>
       </c>
       <c r="W204">
-        <v>9.42</v>
+        <v>2.83</v>
       </c>
       <c r="X204">
         <v>9.42</v>

--- a/public/StageTable.xlsx
+++ b/public/StageTable.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -773,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J5" t="str">
         <v>[[1,1200,100],[3,1020,100],[16,500,100],[19,500,100]]</v>
@@ -813,13 +809,13 @@
       </c>
       <c r="V5">
         <f>Y5/100</f>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W5">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Y5">
         <v>600000</v>
@@ -872,7 +868,7 @@
         <v>2</v>
       </c>
       <c r="I6" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J6" t="str">
         <v>[[1,1400,100],[3,1040,100],[16,550,100],[19,550,100],[500001,1,50],[500101,1,10]]</v>
@@ -912,13 +908,13 @@
       </c>
       <c r="V6">
         <f>Y6/100</f>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W6">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Y6">
         <v>900000</v>
@@ -971,7 +967,7 @@
         <v>3</v>
       </c>
       <c r="I7" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J7" t="str">
         <v>[[1,1600,100],[3,1060,100],[16,582,100],[19,582,100],[500001,1,50],[500101,1,10]]</v>
@@ -1011,13 +1007,13 @@
       </c>
       <c r="V7">
         <f>Y7/100</f>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W7">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Y7">
         <v>1200000</v>
@@ -1070,7 +1066,7 @@
         <v>4</v>
       </c>
       <c r="I8" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J8" t="str">
         <v>[[1,1800,100],[3,1080,100],[16,605,100],[19,605,100],[500001,1,50],[500101,1,10]]</v>
@@ -1110,13 +1106,13 @@
       </c>
       <c r="V8">
         <f>Y8/100</f>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W8">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Y8">
         <v>1600000</v>
@@ -1169,7 +1165,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J9" t="str">
         <v>[[1,2000,100],[3,1100,100],[16,624,100],[19,624,100],[500001,1,50],[500002,1,50],[500101,1,10],[500102,1,10]]</v>
@@ -1209,13 +1205,13 @@
       </c>
       <c r="V9">
         <f>Y9/100</f>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W9">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Y9">
         <v>1800000</v>
@@ -1268,7 +1264,7 @@
         <v>2</v>
       </c>
       <c r="I10" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J10" t="str">
         <v>[[1,2200,100],[3,1120,100],[16,640,100],[19,640,100],[500001,1,50],[500002,1,50],[500101,1,10],[500102,1,10]]</v>
@@ -1308,13 +1304,13 @@
       </c>
       <c r="V10">
         <f>Y10/100</f>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W10">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Y10">
         <v>2400000</v>
@@ -1367,7 +1363,7 @@
         <v>3</v>
       </c>
       <c r="I11" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J11" t="str">
         <v>[[1,2400,100],[3,1140,100],[16,654,100],[19,654,100],[500001,2,50],[500002,1,50],[500101,2,10],[500102,1,10]]</v>
@@ -1407,13 +1403,13 @@
       </c>
       <c r="V11">
         <f>Y11/100</f>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W11">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Y11">
         <v>3000000</v>
@@ -1466,7 +1462,7 @@
         <v>4</v>
       </c>
       <c r="I12" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J12" t="str">
         <v>[[1,2600,100],[3,1160,100],[16,666,100],[19,666,100],[500001,2,50],[500002,1,50],[500101,2,10],[500102,1,10]]</v>
@@ -1506,13 +1502,13 @@
       </c>
       <c r="V12">
         <f>Y12/100</f>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W12">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Y12">
         <v>3600000</v>
@@ -1565,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J13" t="str">
         <v>[[1,2800,100],[3,1180,100],[16,677,100],[19,677,100],[500001,2,50],[500002,1,50],[500101,2,10],[500102,1,10]]</v>
@@ -1605,13 +1601,13 @@
       </c>
       <c r="V13">
         <f>Y13/100</f>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W13">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Y13">
         <v>4800000</v>
@@ -1664,7 +1660,7 @@
         <v>2</v>
       </c>
       <c r="I14" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J14" t="str">
         <v>[[1,3000,100],[3,1200,100],[16,687,100],[19,687,100],[500001,2,50],[500002,2,50],[500101,2,10],[500102,2,10],[500003,1,50],[500103,1,10]]</v>
@@ -1704,13 +1700,13 @@
       </c>
       <c r="V14">
         <f>Y14/100</f>
-        <v>0.43</v>
+        <v>0.86</v>
       </c>
       <c r="W14">
-        <v>0.4</v>
+        <v>0.79</v>
       </c>
       <c r="X14">
-        <v>1.32</v>
+        <v>0.79</v>
       </c>
       <c r="Y14">
         <v>6000000</v>
@@ -1763,7 +1759,7 @@
         <v>3</v>
       </c>
       <c r="I15" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J15" t="str">
         <v>[[1,3200,100],[3,1220,100],[16,696,100],[19,696,100],[500001,2,50],[500002,2,50],[500101,2,10],[500102,2,10],[500003,1,50],[500103,1,10]]</v>
@@ -1803,13 +1799,13 @@
       </c>
       <c r="V15">
         <f>Y15/100</f>
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="W15">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="X15">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="Y15">
         <v>6400000</v>
@@ -1862,7 +1858,7 @@
         <v>4</v>
       </c>
       <c r="I16" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J16" t="str">
         <v>[[1,3400,100],[3,1240,100],[16,705,100],[19,705,100],[500001,2,50],[500002,2,50],[500101,2,10],[500102,2,10],[500003,1,50],[500103,1,10]]</v>
@@ -1902,13 +1898,13 @@
       </c>
       <c r="V16">
         <f>Y16/100</f>
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="W16">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="X16">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="Y16">
         <v>6800000</v>
@@ -1961,7 +1957,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J17" t="str">
         <v>[[1,3600,100],[3,1260,100],[16,712,100],[19,712,100],[500001,2,50],[500002,2,50],[500101,2,10],[500102,2,10],[500003,1,50],[500103,1,10]]</v>
@@ -2001,13 +1997,13 @@
       </c>
       <c r="V17">
         <f>Y17/100</f>
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="W17">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="X17">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="Y17">
         <v>9600000</v>
@@ -2060,7 +2056,7 @@
         <v>2</v>
       </c>
       <c r="I18" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J18" t="str">
         <v>[[1,3801,100],[3,1280,100],[16,720,100],[19,720,100],[500001,2,50],[500002,2,50],[500101,2,10],[500102,2,10],[500003,1,50],[500103,1,10]]</v>
@@ -2100,13 +2096,13 @@
       </c>
       <c r="V18">
         <f>Y18/100</f>
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="W18">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="X18">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="Y18">
         <v>10000000</v>
@@ -2159,7 +2155,7 @@
         <v>3</v>
       </c>
       <c r="I19" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J19" t="str">
         <v>[[1,4001,100],[3,1300,100],[16,727,100],[19,727,100],[500001,2,50],[500002,2,50],[500101,2,10],[500102,2,10],[500003,2,50],[500103,2,10]]</v>
@@ -2199,13 +2195,13 @@
       </c>
       <c r="V19">
         <f>Y19/100</f>
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="W19">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="X19">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="Y19">
         <v>12000000</v>
@@ -2258,7 +2254,7 @@
         <v>4</v>
       </c>
       <c r="I20" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J20" t="str">
         <v>[[1,4201,100],[3,1320,100],[16,733,100],[19,733,100],[500001,2,50],[500002,2,50],[500101,2,10],[500102,2,10],[500003,2,50],[500103,2,10]]</v>
@@ -2298,13 +2294,13 @@
       </c>
       <c r="V20">
         <f>Y20/100</f>
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="W20">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="X20">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="Y20">
         <v>14000000</v>
@@ -2357,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J21" t="str">
         <v>[[1,4401,100],[3,1340,100],[16,739,100],[19,739,100],[500001,3,50],[500002,2,50],[500101,3,10],[500102,2,10],[500003,2,50],[500103,2,10]]</v>
@@ -2397,13 +2393,13 @@
       </c>
       <c r="V21">
         <f>Y21/100</f>
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="W21">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="X21">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="Y21">
         <v>14500000</v>
@@ -2456,7 +2452,7 @@
         <v>2</v>
       </c>
       <c r="I22" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J22" t="str">
         <v>[[1,4601,100],[3,1360,100],[16,745,100],[19,745,100],[500001,3,50],[500002,2,50],[500101,3,10],[500102,2,10],[500003,2,50],[500103,2,10]]</v>
@@ -2496,13 +2492,13 @@
       </c>
       <c r="V22">
         <f>Y22/100</f>
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="W22">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="X22">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="Y22">
         <v>15000000</v>
@@ -2555,7 +2551,7 @@
         <v>3</v>
       </c>
       <c r="I23" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J23" t="str">
         <v>[[1,4801,100],[3,1380,100],[16,751,100],[19,751,100],[500001,3,50],[500002,2,50],[500101,3,10],[500102,2,10],[500003,2,50],[500103,2,10]]</v>
@@ -2595,13 +2591,13 @@
       </c>
       <c r="V23">
         <f>Y23/100</f>
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="W23">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="X23">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="Y23">
         <v>18000000</v>
@@ -2654,7 +2650,7 @@
         <v>4</v>
       </c>
       <c r="I24" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J24" t="str">
         <v>[[1,5001,100],[3,1400,100],[16,756,100],[19,756,100],[500001,3,50],[500002,3,50],[500101,3,10],[500102,3,10],[500003,2,50],[500103,2,10]]</v>
@@ -2694,13 +2690,13 @@
       </c>
       <c r="V24">
         <f>Y24/100</f>
-        <v>0.47</v>
+        <v>0.94</v>
       </c>
       <c r="W24">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="X24">
-        <v>1.45</v>
+        <v>0.87</v>
       </c>
       <c r="Y24">
         <v>18500000</v>
@@ -2753,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J25" t="str">
         <v>[[1,5201,100],[3,1420,100],[16,761,100],[19,761,100],[500001,3,50],[500002,3,50],[500101,3,10],[500102,3,10],[500003,2,50],[500103,2,10]]</v>
@@ -2793,13 +2789,13 @@
       </c>
       <c r="V25">
         <f>Y25/100</f>
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="W25">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="X25">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
       <c r="Y25">
         <v>19000000</v>
@@ -2852,7 +2848,7 @@
         <v>2</v>
       </c>
       <c r="I26" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J26" t="str">
         <v>[[1,5401,100],[3,1440,100],[16,766,100],[19,766,100],[500001,3,50],[500002,3,50],[500101,3,10],[500102,3,10],[500003,2,50],[500103,2,10]]</v>
@@ -2892,13 +2888,13 @@
       </c>
       <c r="V26">
         <f>Y26/100</f>
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="W26">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="X26">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
       <c r="Y26">
         <v>19500000</v>
@@ -2951,7 +2947,7 @@
         <v>3</v>
       </c>
       <c r="I27" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J27" t="str">
         <v>[[1,5601,100],[3,1460,100],[16,771,100],[19,771,100],[500001,3,50],[500002,3,50],[500101,3,10],[500102,3,10],[500003,2,50],[500103,2,10]]</v>
@@ -2991,13 +2987,13 @@
       </c>
       <c r="V27">
         <f>Y27/100</f>
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="W27">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="X27">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
       <c r="Y27">
         <v>22000000</v>
@@ -3050,7 +3046,7 @@
         <v>4</v>
       </c>
       <c r="I28" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J28" t="str">
         <v>[[1,5801,100],[3,1480,100],[16,775,100],[19,775,100],[500001,3,50],[500002,3,50],[500101,3,10],[500102,3,10],[500003,2,50],[500103,2,10]]</v>
@@ -3090,13 +3086,13 @@
       </c>
       <c r="V28">
         <f>Y28/100</f>
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="W28">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="X28">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
       <c r="Y28">
         <v>22500000</v>
@@ -3149,7 +3145,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J29" t="str">
         <v>[[1,6001,100],[3,1500,100],[16,780,100],[19,780,100],[500001,3,50],[500002,3,50],[500101,3,10],[500102,3,10],[500003,3,50],[500103,3,10]]</v>
@@ -3189,13 +3185,13 @@
       </c>
       <c r="V29">
         <f>Y29/100</f>
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="W29">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="X29">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
       <c r="Y29">
         <v>23000000</v>
@@ -3248,7 +3244,7 @@
         <v>2</v>
       </c>
       <c r="I30" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J30" t="str">
         <v>[[1,6201,100],[3,1520,100],[16,784,100],[19,784,100],[500001,3,50],[500002,3,50],[500101,3,10],[500102,3,10],[500003,3,50],[500103,3,10]]</v>
@@ -3288,13 +3284,13 @@
       </c>
       <c r="V30">
         <f>Y30/100</f>
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="W30">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="X30">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
       <c r="Y30">
         <v>26000000</v>
@@ -3347,7 +3343,7 @@
         <v>3</v>
       </c>
       <c r="I31" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J31" t="str">
         <v>[[1,6401,100],[3,1540,100],[16,788,100],[19,788,100],[500001,4,50],[500002,3,50],[500101,4,10],[500102,3,10],[500003,3,50],[500103,3,10]]</v>
@@ -3387,13 +3383,13 @@
       </c>
       <c r="V31">
         <f>Y31/100</f>
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="W31">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="X31">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
       <c r="Y31">
         <v>26500000</v>
@@ -3446,7 +3442,7 @@
         <v>4</v>
       </c>
       <c r="I32" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J32" t="str">
         <v>[[1,6601,100],[3,1560,100],[16,792,100],[19,792,100],[500001,4,50],[500002,3,50],[500101,4,10],[500102,3,10],[500003,3,50],[500103,3,10]]</v>
@@ -3486,13 +3482,13 @@
       </c>
       <c r="V32">
         <f>Y32/100</f>
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="W32">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="X32">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
       <c r="Y32">
         <v>27000000</v>
@@ -3545,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J33" t="str">
         <v>[[1,6801,100],[3,1580,100],[16,796,100],[19,796,100],[500001,4,50],[500002,3,50],[500101,4,10],[500102,3,10],[500003,3,50],[500103,3,10]]</v>
@@ -3585,13 +3581,13 @@
       </c>
       <c r="V33">
         <f>Y33/100</f>
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="W33">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="X33">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
       <c r="Y33">
         <v>30000000</v>
@@ -3644,7 +3640,7 @@
         <v>2</v>
       </c>
       <c r="I34" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J34" t="str">
         <v>[[1,7001,100],[3,1600,100],[16,799,100],[19,799,100],[500001,4,50],[500002,4,50],[500101,4,10],[500102,4,10],[500003,3,50],[500103,3,10]]</v>
@@ -3684,13 +3680,13 @@
       </c>
       <c r="V34">
         <f>Y34/100</f>
-        <v>0.52</v>
+        <v>1.04</v>
       </c>
       <c r="W34">
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="X34">
-        <v>1.6</v>
+        <v>0.96</v>
       </c>
       <c r="Y34">
         <v>30500000</v>
@@ -3743,7 +3739,7 @@
         <v>3</v>
       </c>
       <c r="I35" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J35" t="str">
         <v>[[1,7201,100],[3,1620,100],[16,803,100],[19,803,100],[500001,4,50],[500002,4,50],[500101,4,10],[500102,4,10],[500003,3,50],[500103,3,10]]</v>
@@ -3783,13 +3779,13 @@
       </c>
       <c r="V35">
         <f>Y35/100</f>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W35">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="X35">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="Y35">
         <v>31000000</v>
@@ -3842,7 +3838,7 @@
         <v>4</v>
       </c>
       <c r="I36" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J36" t="str">
         <v>[[1,7401,100],[3,1640,100],[16,807,100],[19,807,100],[500001,4,50],[500002,4,50],[500101,4,10],[500102,4,10],[500003,3,50],[500103,3,10]]</v>
@@ -3882,13 +3878,13 @@
       </c>
       <c r="V36">
         <f>Y36/100</f>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W36">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="X36">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="Y36">
         <v>31500000</v>
@@ -3941,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J37" t="str">
         <v>[[1,7601,100],[3,1660,100],[16,810,100],[19,810,100],[500001,4,50],[500002,4,50],[500101,4,10],[500102,4,10],[500003,3,50],[500103,3,10]]</v>
@@ -3981,13 +3977,13 @@
       </c>
       <c r="V37">
         <f>Y37/100</f>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W37">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="X37">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="Y37">
         <v>34000000</v>
@@ -4040,7 +4036,7 @@
         <v>2</v>
       </c>
       <c r="I38" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J38" t="str">
         <v>[[1,7801,100],[3,1680,100],[16,813,100],[19,813,100],[500001,4,50],[500002,4,50],[500101,4,10],[500102,4,10],[500003,3,50],[500103,3,10]]</v>
@@ -4080,13 +4076,13 @@
       </c>
       <c r="V38">
         <f>Y38/100</f>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W38">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="X38">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="Y38">
         <v>34500000</v>
@@ -4139,7 +4135,7 @@
         <v>3</v>
       </c>
       <c r="I39" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J39" t="str">
         <v>[[1,8001,100],[3,1700,100],[16,817,100],[19,817,100],[500001,4,50],[500002,4,50],[500101,4,10],[500102,4,10],[500003,4,50],[500103,4,10]]</v>
@@ -4179,13 +4175,13 @@
       </c>
       <c r="V39">
         <f>Y39/100</f>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W39">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="X39">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="Y39">
         <v>35000000</v>
@@ -4238,7 +4234,7 @@
         <v>4</v>
       </c>
       <c r="I40" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J40" t="str">
         <v>[[1,8201,100],[3,1720,100],[16,820,100],[19,820,100],[500001,4,50],[500002,4,50],[500101,4,10],[500102,4,10],[500003,4,50],[500103,4,10]]</v>
@@ -4278,13 +4274,13 @@
       </c>
       <c r="V40">
         <f>Y40/100</f>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W40">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="X40">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="Y40">
         <v>38000000</v>
@@ -4337,7 +4333,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J41" t="str">
         <v>[[1,8401,100],[3,1740,100],[16,823,100],[19,823,100],[500001,5,50],[500002,4,50],[500101,5,10],[500102,4,10],[500003,4,50],[500103,4,10]]</v>
@@ -4377,13 +4373,13 @@
       </c>
       <c r="V41">
         <f>Y41/100</f>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W41">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="X41">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="Y41">
         <v>38500000</v>
@@ -4436,7 +4432,7 @@
         <v>2</v>
       </c>
       <c r="I42" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J42" t="str">
         <v>[[1,8601,100],[3,1760,100],[16,826,100],[19,826,100],[500001,5,50],[500002,4,50],[500101,5,10],[500102,4,10],[500003,4,50],[500103,4,10]]</v>
@@ -4476,13 +4472,13 @@
       </c>
       <c r="V42">
         <f>Y42/100</f>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W42">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="X42">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="Y42">
         <v>39000000</v>
@@ -4535,7 +4531,7 @@
         <v>3</v>
       </c>
       <c r="I43" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J43" t="str">
         <v>[[1,8802,100],[3,1780,100],[16,829,100],[19,829,100],[500001,5,50],[500002,4,50],[500101,5,10],[500102,4,10],[500003,4,50],[500103,4,10]]</v>
@@ -4575,13 +4571,13 @@
       </c>
       <c r="V43">
         <f>Y43/100</f>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W43">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="X43">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="Y43">
         <v>42000000</v>
@@ -4634,7 +4630,7 @@
         <v>4</v>
       </c>
       <c r="I44" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J44" t="str">
         <v>[[1,9002,100],[3,1800,100],[16,832,100],[19,832,100],[500001,5,50],[500002,5,50],[500101,5,10],[500102,5,10],[500003,4,50],[500103,4,10]]</v>
@@ -4674,13 +4670,13 @@
       </c>
       <c r="V44">
         <f>Y44/100</f>
-        <v>0.57</v>
+        <v>1.14</v>
       </c>
       <c r="W44">
-        <v>0.53</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
-        <v>1.76</v>
+        <v>1.05</v>
       </c>
       <c r="Y44">
         <v>42500000</v>
@@ -4733,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J45" t="str">
         <v>[[1,9202,100],[3,1820,100],[16,835,100],[19,835,100],[500001,5,50],[500002,5,50],[500101,5,10],[500102,5,10],[500003,4,50],[500103,4,10]]</v>
@@ -4773,13 +4769,13 @@
       </c>
       <c r="V45">
         <f>Y45/100</f>
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="W45">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="X45">
-        <v>1.46</v>
+        <v>0.88</v>
       </c>
       <c r="Y45">
         <v>44000000</v>
@@ -4832,7 +4828,7 @@
         <v>2</v>
       </c>
       <c r="I46" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J46" t="str">
         <v>[[1,9402,100],[3,1840,100],[16,837,100],[19,837,100],[500001,5,50],[500002,5,50],[500101,5,10],[500102,5,10],[500003,4,50],[500103,4,10]]</v>
@@ -4872,13 +4868,13 @@
       </c>
       <c r="V46">
         <f>Y46/100</f>
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="W46">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="X46">
-        <v>1.46</v>
+        <v>0.88</v>
       </c>
       <c r="Y46">
         <v>44500000</v>
@@ -4931,7 +4927,7 @@
         <v>3</v>
       </c>
       <c r="I47" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J47" t="str">
         <v>[[1,9602,100],[3,1860,100],[16,840,100],[19,840,100],[500001,5,50],[500002,5,50],[500101,5,10],[500102,5,10],[500003,4,50],[500103,4,10]]</v>
@@ -4971,13 +4967,13 @@
       </c>
       <c r="V47">
         <f>Y47/100</f>
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="W47">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="X47">
-        <v>1.46</v>
+        <v>0.88</v>
       </c>
       <c r="Y47">
         <v>50000000</v>
@@ -5030,7 +5026,7 @@
         <v>4</v>
       </c>
       <c r="I48" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J48" t="str">
         <v>[[1,9802,100],[3,1880,100],[16,843,100],[19,843,100],[500001,5,50],[500002,5,50],[500101,5,10],[500102,5,10],[500003,4,50],[500103,4,10]]</v>
@@ -5070,13 +5066,13 @@
       </c>
       <c r="V48">
         <f>Y48/100</f>
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="W48">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="X48">
-        <v>1.46</v>
+        <v>0.88</v>
       </c>
       <c r="Y48">
         <v>52000000</v>
@@ -5129,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J49" t="str">
         <v>[[1,10002,100],[3,1900,100],[16,845,100],[19,845,100],[500001,5,50],[500002,5,50],[500101,5,10],[500102,5,10],[500003,5,50],[500103,5,10]]</v>
@@ -5169,13 +5165,13 @@
       </c>
       <c r="V49">
         <f>Y49/100</f>
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="W49">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="X49">
-        <v>1.46</v>
+        <v>0.88</v>
       </c>
       <c r="Y49">
         <v>52500000</v>
@@ -5228,7 +5224,7 @@
         <v>2</v>
       </c>
       <c r="I50" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J50" t="str">
         <v>[[1,10202,100],[3,1920,100],[16,848,100],[19,848,100],[500001,5,50],[500002,5,50],[500101,5,10],[500102,5,10],[500003,5,50],[500103,5,10]]</v>
@@ -5268,13 +5264,13 @@
       </c>
       <c r="V50">
         <f>Y50/100</f>
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="W50">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="X50">
-        <v>1.46</v>
+        <v>0.88</v>
       </c>
       <c r="Y50">
         <v>58000000</v>
@@ -5327,7 +5323,7 @@
         <v>3</v>
       </c>
       <c r="I51" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J51" t="str">
         <v>[[1,10402,100],[3,1940,100],[16,851,100],[19,851,100],[500001,6,50],[500002,5,50],[500101,6,10],[500102,5,10],[500003,5,50],[500103,5,10]]</v>
@@ -5367,13 +5363,13 @@
       </c>
       <c r="V51">
         <f>Y51/100</f>
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="W51">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="X51">
-        <v>1.46</v>
+        <v>0.88</v>
       </c>
       <c r="Y51">
         <v>58500000</v>
@@ -5426,7 +5422,7 @@
         <v>4</v>
       </c>
       <c r="I52" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J52" t="str">
         <v>[[1,10602,100],[3,1960,100],[16,853,100],[19,853,100],[500001,6,50],[500002,5,50],[500101,6,10],[500102,5,10],[500003,5,50],[500103,5,10]]</v>
@@ -5466,13 +5462,13 @@
       </c>
       <c r="V52">
         <f>Y52/100</f>
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="W52">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="X52">
-        <v>1.46</v>
+        <v>0.88</v>
       </c>
       <c r="Y52">
         <v>59000000</v>
@@ -5525,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J53" t="str">
         <v>[[1,10802,100],[3,1980,100],[16,855,100],[19,855,100],[500001,6,50],[500002,5,50],[500101,6,10],[500102,5,10],[500003,5,50],[500103,5,10]]</v>
@@ -5565,13 +5561,13 @@
       </c>
       <c r="V53">
         <f>Y53/100</f>
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="W53">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="X53">
-        <v>1.46</v>
+        <v>0.88</v>
       </c>
       <c r="Y53">
         <v>64000000</v>
@@ -5624,7 +5620,7 @@
         <v>2</v>
       </c>
       <c r="I54" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J54" t="str">
         <v>[[1,11002,100],[3,2000,100],[16,858,100],[19,858,100],[500001,6,50],[500002,6,50],[500101,6,10],[500102,6,10],[500003,5,50],[500103,5,10]]</v>
@@ -5664,13 +5660,13 @@
       </c>
       <c r="V54">
         <f>Y54/100</f>
-        <v>0.77</v>
+        <v>1.55</v>
       </c>
       <c r="W54">
-        <v>0.68</v>
+        <v>1.35</v>
       </c>
       <c r="X54">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="Y54">
         <v>68000000</v>
@@ -5723,7 +5719,7 @@
         <v>3</v>
       </c>
       <c r="I55" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J55" t="str">
         <v>[[1,11202,100],[3,2020,100],[16,860,100],[19,860,100],[500001,6,50],[500002,6,50],[500101,6,10],[500102,6,10],[500003,5,50],[500103,5,10]]</v>
@@ -5763,13 +5759,13 @@
       </c>
       <c r="V55">
         <f>Y55/100</f>
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="W55">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="X55">
-        <v>1.61</v>
+        <v>0.97</v>
       </c>
       <c r="Y55">
         <v>68500000</v>
@@ -5822,7 +5818,7 @@
         <v>4</v>
       </c>
       <c r="I56" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J56" t="str">
         <v>[[1,11402,100],[3,2040,100],[16,863,100],[19,863,100],[500001,6,50],[500002,6,50],[500101,6,10],[500102,6,10],[500003,5,50],[500103,5,10]]</v>
@@ -5862,13 +5858,13 @@
       </c>
       <c r="V56">
         <f>Y56/100</f>
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="W56">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="X56">
-        <v>1.61</v>
+        <v>0.97</v>
       </c>
       <c r="Y56">
         <v>70000000</v>
@@ -5921,7 +5917,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J57" t="str">
         <v>[[1,11602,100],[3,2060,100],[16,865,100],[19,865,100],[500001,6,50],[500002,6,50],[500101,6,10],[500102,6,10],[500003,5,50],[500103,5,10]]</v>
@@ -5961,13 +5957,13 @@
       </c>
       <c r="V57">
         <f>Y57/100</f>
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="W57">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="X57">
-        <v>1.61</v>
+        <v>0.97</v>
       </c>
       <c r="Y57">
         <v>78000000</v>
@@ -6020,7 +6016,7 @@
         <v>2</v>
       </c>
       <c r="I58" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J58" t="str">
         <v>[[1,11802,100],[3,2080,100],[16,867,100],[19,867,100],[500001,6,50],[500002,6,50],[500101,6,10],[500102,6,10],[500003,5,50],[500103,5,10]]</v>
@@ -6060,13 +6056,13 @@
       </c>
       <c r="V58">
         <f>Y58/100</f>
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="W58">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="X58">
-        <v>1.61</v>
+        <v>0.97</v>
       </c>
       <c r="Y58">
         <v>80000000</v>
@@ -6119,7 +6115,7 @@
         <v>3</v>
       </c>
       <c r="I59" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J59" t="str">
         <v>[[1,12002,100],[3,2100,100],[16,869,100],[19,869,100],[500001,6,50],[500002,6,50],[500101,6,10],[500102,6,10],[500003,6,50],[500103,6,10]]</v>
@@ -6159,13 +6155,13 @@
       </c>
       <c r="V59">
         <f>Y59/100</f>
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="W59">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="X59">
-        <v>1.61</v>
+        <v>0.97</v>
       </c>
       <c r="Y59">
         <v>80500000</v>
@@ -6218,7 +6214,7 @@
         <v>4</v>
       </c>
       <c r="I60" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J60" t="str">
         <v>[[1,12202,100],[3,2120,100],[16,871,100],[19,871,100],[500001,6,50],[500002,6,50],[500101,6,10],[500102,6,10],[500003,6,50],[500103,6,10]]</v>
@@ -6258,13 +6254,13 @@
       </c>
       <c r="V60">
         <f>Y60/100</f>
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="W60">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="X60">
-        <v>1.61</v>
+        <v>0.97</v>
       </c>
       <c r="Y60">
         <v>90000000</v>
@@ -6317,7 +6313,7 @@
         <v>1</v>
       </c>
       <c r="I61" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J61" t="str">
         <v>[[1,12402,100],[3,2140,100],[16,874,100],[19,874,100],[500001,7,50],[500002,6,50],[500101,7,10],[500102,6,10],[500003,6,50],[500103,6,10]]</v>
@@ -6357,13 +6353,13 @@
       </c>
       <c r="V61">
         <f>Y61/100</f>
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="W61">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="X61">
-        <v>1.61</v>
+        <v>0.97</v>
       </c>
       <c r="Y61">
         <v>90500000</v>
@@ -6416,7 +6412,7 @@
         <v>2</v>
       </c>
       <c r="I62" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J62" t="str">
         <v>[[1,12602,100],[3,2160,100],[16,876,100],[19,876,100],[500001,7,50],[500002,6,50],[500101,7,10],[500102,6,10],[500003,6,50],[500103,6,10]]</v>
@@ -6456,13 +6452,13 @@
       </c>
       <c r="V62">
         <f>Y62/100</f>
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="W62">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="X62">
-        <v>1.61</v>
+        <v>0.97</v>
       </c>
       <c r="Y62">
         <v>92000000</v>
@@ -6515,7 +6511,7 @@
         <v>3</v>
       </c>
       <c r="I63" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J63" t="str">
         <v>[[1,12802,100],[3,2180,100],[16,878,100],[19,878,100],[500001,7,50],[500002,6,50],[500101,7,10],[500102,6,10],[500003,6,50],[500103,6,10]]</v>
@@ -6555,13 +6551,13 @@
       </c>
       <c r="V63">
         <f>Y63/100</f>
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="W63">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="X63">
-        <v>1.61</v>
+        <v>0.97</v>
       </c>
       <c r="Y63">
         <v>100000000</v>
@@ -6614,7 +6610,7 @@
         <v>4</v>
       </c>
       <c r="I64" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J64" t="str">
         <v>[[1,13002,100],[3,2200,100],[16,880,100],[19,880,100],[500001,7,50],[500002,7,50],[500101,7,10],[500102,7,10],[500003,6,50],[500103,6,10]]</v>
@@ -6654,13 +6650,13 @@
       </c>
       <c r="V64">
         <f>Y64/100</f>
-        <v>0.69</v>
+        <v>1.38</v>
       </c>
       <c r="W64">
-        <v>0.64</v>
+        <v>1.28</v>
       </c>
       <c r="X64">
-        <v>2.13</v>
+        <v>1.28</v>
       </c>
       <c r="Y64">
         <v>120000000</v>
@@ -6713,7 +6709,7 @@
         <v>1</v>
       </c>
       <c r="I65" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J65" t="str">
         <v>[[1,13202,100],[3,2220,100],[16,882,100],[19,882,100],[500001,7,50],[500002,7,50],[500101,7,10],[500102,7,10],[500003,6,50],[500103,6,10]]</v>
@@ -6753,13 +6749,13 @@
       </c>
       <c r="V65">
         <f>Y65/100</f>
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="W65">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="X65">
-        <v>1.77</v>
+        <v>1.06</v>
       </c>
       <c r="Y65">
         <v>125000000</v>
@@ -6812,7 +6808,7 @@
         <v>2</v>
       </c>
       <c r="I66" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J66" t="str">
         <v>[[1,13402,100],[3,2240,100],[16,884,100],[19,884,100],[500001,7,50],[500002,7,50],[500101,7,10],[500102,7,10],[500003,6,50],[500103,6,10]]</v>
@@ -6852,13 +6848,13 @@
       </c>
       <c r="V66">
         <f>Y66/100</f>
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="W66">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
-        <v>1.77</v>
+        <v>1.06</v>
       </c>
       <c r="Y66">
         <v>130000000</v>
@@ -6911,7 +6907,7 @@
         <v>3</v>
       </c>
       <c r="I67" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J67" t="str">
         <v>[[1,13602,100],[3,2260,100],[16,886,100],[19,886,100],[500001,7,50],[500002,7,50],[500101,7,10],[500102,7,10],[500003,6,50],[500103,6,10]]</v>
@@ -6951,13 +6947,13 @@
       </c>
       <c r="V67">
         <f>Y67/100</f>
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="W67">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1.77</v>
+        <v>1.06</v>
       </c>
       <c r="Y67">
         <v>135000000</v>
@@ -7010,7 +7006,7 @@
         <v>4</v>
       </c>
       <c r="I68" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J68" t="str">
         <v>[[1,13803,100],[3,2279,100],[16,888,100],[19,888,100],[500001,7,50],[500002,7,50],[500101,7,10],[500102,7,10],[500003,6,50],[500103,6,10]]</v>
@@ -7050,13 +7046,13 @@
       </c>
       <c r="V68">
         <f>Y68/100</f>
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="W68">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
-        <v>1.77</v>
+        <v>1.06</v>
       </c>
       <c r="Y68">
         <v>140000000</v>
@@ -7109,7 +7105,7 @@
         <v>1</v>
       </c>
       <c r="I69" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J69" t="str">
         <v>[[1,14003,100],[3,2299,100],[16,890,100],[19,890,100],[500001,7,50],[500002,7,50],[500101,7,10],[500102,7,10],[500003,7,50],[500103,7,10]]</v>
@@ -7149,13 +7145,13 @@
       </c>
       <c r="V69">
         <f>Y69/100</f>
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="W69">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="X69">
-        <v>1.77</v>
+        <v>1.06</v>
       </c>
       <c r="Y69">
         <v>145000000</v>
@@ -7208,7 +7204,7 @@
         <v>2</v>
       </c>
       <c r="I70" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J70" t="str">
         <v>[[1,14203,100],[3,2319,100],[16,891,100],[19,891,100],[500001,7,50],[500002,7,50],[500101,7,10],[500102,7,10],[500003,7,50],[500103,7,10]]</v>
@@ -7248,13 +7244,13 @@
       </c>
       <c r="V70">
         <f>Y70/100</f>
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="W70">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="X70">
-        <v>1.77</v>
+        <v>1.06</v>
       </c>
       <c r="Y70">
         <v>150000000</v>
@@ -7307,7 +7303,7 @@
         <v>3</v>
       </c>
       <c r="I71" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J71" t="str">
         <v>[[1,14403,100],[3,2339,100],[16,893,100],[19,893,100],[500001,8,50],[500002,7,50],[500101,8,10],[500102,7,10],[500003,7,50],[500103,7,10]]</v>
@@ -7347,13 +7343,13 @@
       </c>
       <c r="V71">
         <f>Y71/100</f>
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="W71">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="X71">
-        <v>1.77</v>
+        <v>1.06</v>
       </c>
       <c r="Y71">
         <v>155000000</v>
@@ -7406,7 +7402,7 @@
         <v>4</v>
       </c>
       <c r="I72" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J72" t="str">
         <v>[[1,14603,100],[3,2359,100],[16,895,100],[19,895,100],[500001,8,50],[500002,7,50],[500101,8,10],[500102,7,10],[500003,7,50],[500103,7,10]]</v>
@@ -7446,13 +7442,13 @@
       </c>
       <c r="V72">
         <f>Y72/100</f>
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="W72">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1.77</v>
+        <v>1.06</v>
       </c>
       <c r="Y72">
         <v>160000000</v>
@@ -7505,7 +7501,7 @@
         <v>1</v>
       </c>
       <c r="I73" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J73" t="str">
         <v>[[1,14803,100],[3,2379,100],[16,897,100],[19,897,100],[500001,8,50],[500002,7,50],[500101,8,10],[500102,7,10],[500003,7,50],[500103,7,10]]</v>
@@ -7545,13 +7541,13 @@
       </c>
       <c r="V73">
         <f>Y73/100</f>
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="W73">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="X73">
-        <v>1.77</v>
+        <v>1.06</v>
       </c>
       <c r="Y73">
         <v>165000000</v>
@@ -7604,7 +7600,7 @@
         <v>2</v>
       </c>
       <c r="I74" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J74" t="str">
         <v>[[1,15003,100],[3,2399,100],[16,899,100],[19,899,100],[500001,8,50],[500002,8,50],[500101,8,10],[500102,8,10],[500003,7,50],[500103,7,10]]</v>
@@ -7644,13 +7640,13 @@
       </c>
       <c r="V74">
         <f>Y74/100</f>
-        <v>0.76</v>
+        <v>1.52</v>
       </c>
       <c r="W74">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="X74">
-        <v>2.34</v>
+        <v>1.4</v>
       </c>
       <c r="Y74">
         <v>170000000</v>
@@ -7703,7 +7699,7 @@
         <v>3</v>
       </c>
       <c r="I75" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J75" t="str">
         <v>[[1,15203,100],[3,2419,100],[16,900,100],[19,900,100],[500001,8,50],[500002,8,50],[500101,8,10],[500102,8,10],[500003,7,50],[500103,7,10]]</v>
@@ -7743,13 +7739,13 @@
       </c>
       <c r="V75">
         <f>Y75/100</f>
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="W75">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="X75">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="Y75">
         <v>175000000</v>
@@ -7802,7 +7798,7 @@
         <v>4</v>
       </c>
       <c r="I76" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J76" t="str">
         <v>[[1,15403,100],[3,2439,100],[16,902,100],[19,902,100],[500001,8,50],[500002,8,50],[500101,8,10],[500102,8,10],[500003,7,50],[500103,7,10]]</v>
@@ -7842,13 +7838,13 @@
       </c>
       <c r="V76">
         <f>Y76/100</f>
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="W76">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="X76">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="Y76">
         <v>180000000</v>
@@ -7901,7 +7897,7 @@
         <v>1</v>
       </c>
       <c r="I77" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J77" t="str">
         <v>[[1,15603,100],[3,2459,100],[16,904,100],[19,904,100],[500001,8,50],[500002,8,50],[500101,8,10],[500102,8,10],[500003,7,50],[500103,7,10]]</v>
@@ -7941,13 +7937,13 @@
       </c>
       <c r="V77">
         <f>Y77/100</f>
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="W77">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="X77">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="Y77">
         <v>200000000</v>
@@ -8000,7 +7996,7 @@
         <v>2</v>
       </c>
       <c r="I78" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J78" t="str">
         <v>[[1,15803,100],[3,2479,100],[16,906,100],[19,906,100],[500001,8,50],[500002,8,50],[500101,8,10],[500102,8,10],[500003,7,50],[500103,7,10]]</v>
@@ -8040,13 +8036,13 @@
       </c>
       <c r="V78">
         <f>Y78/100</f>
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="W78">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="X78">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="Y78">
         <v>205000000</v>
@@ -8099,7 +8095,7 @@
         <v>3</v>
       </c>
       <c r="I79" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J79" t="str">
         <v>[[1,16003,100],[3,2499,100],[16,907,100],[19,907,100],[500001,8,50],[500002,8,50],[500101,8,10],[500102,8,10],[500003,8,50],[500103,8,10]]</v>
@@ -8139,13 +8135,13 @@
       </c>
       <c r="V79">
         <f>Y79/100</f>
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="W79">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="X79">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="Y79">
         <v>210000000</v>
@@ -8198,7 +8194,7 @@
         <v>4</v>
       </c>
       <c r="I80" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J80" t="str">
         <v>[[1,16203,100],[3,2519,100],[16,909,100],[19,909,100],[500001,8,50],[500002,8,50],[500101,8,10],[500102,8,10],[500003,8,50],[500103,8,10]]</v>
@@ -8238,13 +8234,13 @@
       </c>
       <c r="V80">
         <f>Y80/100</f>
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="W80">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="X80">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="Y80">
         <v>215000000</v>
@@ -8297,7 +8293,7 @@
         <v>1</v>
       </c>
       <c r="I81" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J81" t="str">
         <v>[[1,16403,100],[3,2539,100],[16,911,100],[19,911,100],[500001,9,50],[500002,8,50],[500101,9,10],[500102,8,10],[500003,8,50],[500103,8,10]]</v>
@@ -8337,13 +8333,13 @@
       </c>
       <c r="V81">
         <f>Y81/100</f>
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="W81">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="X81">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="Y81">
         <v>220000000</v>
@@ -8396,7 +8392,7 @@
         <v>2</v>
       </c>
       <c r="I82" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J82" t="str">
         <v>[[1,16603,100],[3,2559,100],[16,912,100],[19,912,100],[500001,9,50],[500002,8,50],[500101,9,10],[500102,8,10],[500003,8,50],[500103,8,10]]</v>
@@ -8436,13 +8432,13 @@
       </c>
       <c r="V82">
         <f>Y82/100</f>
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="W82">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="X82">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="Y82">
         <v>225000000</v>
@@ -8495,7 +8491,7 @@
         <v>3</v>
       </c>
       <c r="I83" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J83" t="str">
         <v>[[1,16803,100],[3,2579,100],[16,914,100],[19,914,100],[500001,9,50],[500002,8,50],[500101,9,10],[500102,8,10],[500003,8,50],[500103,8,10]]</v>
@@ -8535,13 +8531,13 @@
       </c>
       <c r="V83">
         <f>Y83/100</f>
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="W83">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="X83">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="Y83">
         <v>240000000</v>
@@ -8594,7 +8590,7 @@
         <v>4</v>
       </c>
       <c r="I84" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J84" t="str">
         <v>[[1,17003,100],[3,2599,100],[16,915,100],[19,915,100],[500001,9,50],[500002,9,50],[500101,9,10],[500102,9,10],[500003,8,50],[500103,8,10]]</v>
@@ -8634,13 +8630,13 @@
       </c>
       <c r="V84">
         <f>Y84/100</f>
-        <v>0.84</v>
+        <v>1.67</v>
       </c>
       <c r="W84">
-        <v>0.77</v>
+        <v>1.54</v>
       </c>
       <c r="X84">
-        <v>2.57</v>
+        <v>1.54</v>
       </c>
       <c r="Y84">
         <v>260000000</v>
@@ -8693,7 +8689,7 @@
         <v>1</v>
       </c>
       <c r="I85" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J85" t="str">
         <v>[[1,17203,100],[3,2619,100],[16,917,100],[19,917,100],[500001,9,50],[500002,9,50],[500101,9,10],[500102,9,10],[500003,8,50],[500103,8,10]]</v>
@@ -8733,13 +8729,13 @@
       </c>
       <c r="V85">
         <f>Y85/100</f>
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="W85">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="X85">
-        <v>2.14</v>
+        <v>1.29</v>
       </c>
       <c r="Y85">
         <v>265000000</v>
@@ -8792,7 +8788,7 @@
         <v>2</v>
       </c>
       <c r="I86" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J86" t="str">
         <v>[[1,17403,100],[3,2639,100],[16,918,100],[19,918,100],[500001,9,50],[500002,9,50],[500101,9,10],[500102,9,10],[500003,8,50],[500103,8,10]]</v>
@@ -8832,13 +8828,13 @@
       </c>
       <c r="V86">
         <f>Y86/100</f>
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="W86">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="X86">
-        <v>2.14</v>
+        <v>1.29</v>
       </c>
       <c r="Y86">
         <v>270000000</v>
@@ -8891,7 +8887,7 @@
         <v>3</v>
       </c>
       <c r="I87" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J87" t="str">
         <v>[[1,17603,100],[3,2659,100],[16,920,100],[19,920,100],[500001,9,50],[500002,9,50],[500101,9,10],[500102,9,10],[500003,8,50],[500103,8,10]]</v>
@@ -8931,13 +8927,13 @@
       </c>
       <c r="V87">
         <f>Y87/100</f>
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="W87">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="X87">
-        <v>2.14</v>
+        <v>1.29</v>
       </c>
       <c r="Y87">
         <v>280000000</v>
@@ -8990,7 +8986,7 @@
         <v>4</v>
       </c>
       <c r="I88" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J88" t="str">
         <v>[[1,17803,100],[3,2679,100],[16,922,100],[19,922,100],[500001,9,50],[500002,9,50],[500101,9,10],[500102,9,10],[500003,8,50],[500103,8,10]]</v>
@@ -9030,13 +9026,13 @@
       </c>
       <c r="V88">
         <f>Y88/100</f>
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="W88">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="X88">
-        <v>2.14</v>
+        <v>1.29</v>
       </c>
       <c r="Y88">
         <v>300000000</v>
@@ -9089,7 +9085,7 @@
         <v>1</v>
       </c>
       <c r="I89" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J89" t="str">
         <v>[[1,18003,100],[3,2699,100],[16,923,100],[19,923,100],[500001,9,50],[500002,9,50],[500101,9,10],[500102,9,10],[500003,9,50],[500103,9,10]]</v>
@@ -9129,13 +9125,13 @@
       </c>
       <c r="V89">
         <f>Y89/100</f>
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="W89">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="X89">
-        <v>2.14</v>
+        <v>1.29</v>
       </c>
       <c r="Y89">
         <v>305000000</v>
@@ -9188,7 +9184,7 @@
         <v>2</v>
       </c>
       <c r="I90" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J90" t="str">
         <v>[[1,18203,100],[3,2719,100],[16,925,100],[19,925,100],[500001,9,50],[500002,9,50],[500101,9,10],[500102,9,10],[500003,9,50],[500103,9,10]]</v>
@@ -9228,13 +9224,13 @@
       </c>
       <c r="V90">
         <f>Y90/100</f>
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="W90">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="X90">
-        <v>2.14</v>
+        <v>1.29</v>
       </c>
       <c r="Y90">
         <v>320000000</v>
@@ -9287,7 +9283,7 @@
         <v>3</v>
       </c>
       <c r="I91" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J91" t="str">
         <v>[[1,18403,100],[3,2739,100],[16,926,100],[19,926,100],[500001,10,50],[500002,9,50],[500101,10,10],[500102,9,10],[500003,9,50],[500103,9,10]]</v>
@@ -9327,13 +9323,13 @@
       </c>
       <c r="V91">
         <f>Y91/100</f>
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="W91">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="X91">
-        <v>2.14</v>
+        <v>1.29</v>
       </c>
       <c r="Y91">
         <v>325000000</v>
@@ -9386,7 +9382,7 @@
         <v>4</v>
       </c>
       <c r="I92" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J92" t="str">
         <v>[[1,18603,100],[3,2759,100],[16,927,100],[19,927,100],[500001,10,50],[500002,9,50],[500101,10,10],[500102,9,10],[500003,9,50],[500103,9,10]]</v>
@@ -9426,13 +9422,13 @@
       </c>
       <c r="V92">
         <f>Y92/100</f>
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="W92">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="X92">
-        <v>2.14</v>
+        <v>1.29</v>
       </c>
       <c r="Y92">
         <v>330000000</v>
@@ -9485,7 +9481,7 @@
         <v>1</v>
       </c>
       <c r="I93" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J93" t="str">
         <v>[[1,18804,100],[3,2779,100],[16,929,100],[19,929,100],[500001,10,50],[500002,9,50],[500101,10,10],[500102,9,10],[500003,9,50],[500103,9,10]]</v>
@@ -9525,13 +9521,13 @@
       </c>
       <c r="V93">
         <f>Y93/100</f>
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="W93">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="X93">
-        <v>2.14</v>
+        <v>1.29</v>
       </c>
       <c r="Y93">
         <v>360000000</v>
@@ -9584,7 +9580,7 @@
         <v>2</v>
       </c>
       <c r="I94" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J94" t="str">
         <v>[[1,19004,100],[3,2799,100],[16,930,100],[19,930,100],[500001,10,50],[500002,10,50],[500101,10,10],[500102,10,10],[500003,9,50],[500103,9,10]]</v>
@@ -9624,13 +9620,13 @@
       </c>
       <c r="V94">
         <f>Y94/100</f>
-        <v>0.92</v>
+        <v>1.84</v>
       </c>
       <c r="W94">
-        <v>0.85</v>
+        <v>1.7</v>
       </c>
       <c r="X94">
-        <v>2.83</v>
+        <v>1.7</v>
       </c>
       <c r="Y94">
         <v>380000000</v>
@@ -9683,7 +9679,7 @@
         <v>3</v>
       </c>
       <c r="I95" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J95" t="str">
         <v>[[1,19204,100],[3,2819,100],[16,932,100],[19,932,100],[500001,10,50],[500002,10,50],[500101,10,10],[500102,10,10],[500003,9,50],[500103,9,10]]</v>
@@ -9723,13 +9719,13 @@
       </c>
       <c r="V95">
         <f>Y95/100</f>
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="W95">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="X95">
-        <v>2.36</v>
+        <v>1.41</v>
       </c>
       <c r="Y95">
         <v>385000000</v>
@@ -9782,7 +9778,7 @@
         <v>4</v>
       </c>
       <c r="I96" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J96" t="str">
         <v>[[1,19404,100],[3,2839,100],[16,933,100],[19,933,100],[500001,10,50],[500002,10,50],[500101,10,10],[500102,10,10],[500003,9,50],[500103,9,10]]</v>
@@ -9822,13 +9818,13 @@
       </c>
       <c r="V96">
         <f>Y96/100</f>
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="W96">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="X96">
-        <v>2.36</v>
+        <v>1.41</v>
       </c>
       <c r="Y96">
         <v>390000000</v>
@@ -9881,7 +9877,7 @@
         <v>1</v>
       </c>
       <c r="I97" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J97" t="str">
         <v>[[1,19604,100],[3,2859,100],[16,935,100],[19,935,100],[500001,10,50],[500002,10,50],[500101,10,10],[500102,10,10],[500003,9,50],[500103,9,10]]</v>
@@ -9921,13 +9917,13 @@
       </c>
       <c r="V97">
         <f>Y97/100</f>
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="W97">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="X97">
-        <v>2.36</v>
+        <v>1.41</v>
       </c>
       <c r="Y97">
         <v>420000000</v>
@@ -9980,7 +9976,7 @@
         <v>2</v>
       </c>
       <c r="I98" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J98" t="str">
         <v>[[1,19804,100],[3,2879,100],[16,936,100],[19,936,100],[500001,10,50],[500002,10,50],[500101,10,10],[500102,10,10],[500003,9,50],[500103,9,10]]</v>
@@ -10020,13 +10016,13 @@
       </c>
       <c r="V98">
         <f>Y98/100</f>
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="W98">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="X98">
-        <v>2.36</v>
+        <v>1.41</v>
       </c>
       <c r="Y98">
         <v>440000000</v>
@@ -10079,7 +10075,7 @@
         <v>3</v>
       </c>
       <c r="I99" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J99" t="str">
         <v>[[1,20004,100],[3,2899,100],[16,937,100],[19,937,100],[500001,10,50],[500002,10,50],[500101,10,10],[500102,10,10],[500003,10,50],[500103,10,10]]</v>
@@ -10119,13 +10115,13 @@
       </c>
       <c r="V99">
         <f>Y99/100</f>
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="W99">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="X99">
-        <v>2.36</v>
+        <v>1.41</v>
       </c>
       <c r="Y99">
         <v>445000000</v>
@@ -10178,7 +10174,7 @@
         <v>4</v>
       </c>
       <c r="I100" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J100" t="str">
         <v>[[1,20204,100],[3,2919,100],[16,939,100],[19,939,100],[500001,10,50],[500002,10,50],[500101,10,10],[500102,10,10],[500003,10,50],[500103,10,10]]</v>
@@ -10218,13 +10214,13 @@
       </c>
       <c r="V100">
         <f>Y100/100</f>
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="W100">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="X100">
-        <v>2.36</v>
+        <v>1.41</v>
       </c>
       <c r="Y100">
         <v>480000000</v>
@@ -10277,7 +10273,7 @@
         <v>1</v>
       </c>
       <c r="I101" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J101" t="str">
         <v>[[1,20404,100],[3,2939,100],[16,940,100],[19,940,100],[500001,11,50],[500002,10,50],[500101,11,10],[500102,10,10],[500003,10,50],[500103,10,10]]</v>
@@ -10317,13 +10313,13 @@
       </c>
       <c r="V101">
         <f>Y101/100</f>
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="W101">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="X101">
-        <v>2.36</v>
+        <v>1.41</v>
       </c>
       <c r="Y101">
         <v>485000000</v>
@@ -10376,7 +10372,7 @@
         <v>2</v>
       </c>
       <c r="I102" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J102" t="str">
         <v>[[1,20604,100],[3,2959,100],[16,941,100],[19,941,100],[500001,11,50],[500002,10,50],[500101,11,10],[500102,10,10],[500003,10,50],[500103,10,10]]</v>
@@ -10416,13 +10412,13 @@
       </c>
       <c r="V102">
         <f>Y102/100</f>
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="W102">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="X102">
-        <v>2.36</v>
+        <v>1.41</v>
       </c>
       <c r="Y102">
         <v>490000000</v>
@@ -10475,7 +10471,7 @@
         <v>3</v>
       </c>
       <c r="I103" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J103" t="str">
         <v>[[1,20804,100],[3,2979,100],[16,943,100],[19,943,100],[500001,11,50],[500002,10,50],[500101,11,10],[500102,10,10],[500003,10,50],[500103,10,10]]</v>
@@ -10515,13 +10511,13 @@
       </c>
       <c r="V103">
         <f>Y103/100</f>
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="W103">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="X103">
-        <v>2.36</v>
+        <v>1.41</v>
       </c>
       <c r="Y103">
         <v>540000000</v>
@@ -10574,7 +10570,7 @@
         <v>4</v>
       </c>
       <c r="I104" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J104" t="str">
         <v>[[1,21004,100],[3,2999,100],[16,944,100],[19,944,100],[500001,11,50],[500002,11,50],[500101,11,10],[500102,11,10],[500003,10,50],[500103,10,10]]</v>
@@ -10614,13 +10610,13 @@
       </c>
       <c r="V104">
         <f>Y104/100</f>
-        <v>1.24</v>
+        <v>2.49</v>
       </c>
       <c r="W104">
-        <v>1.09</v>
+        <v>2.18</v>
       </c>
       <c r="X104">
-        <v>3.63</v>
+        <v>2.18</v>
       </c>
       <c r="Y104">
         <v>545000000</v>
@@ -10673,7 +10669,7 @@
         <v>1</v>
       </c>
       <c r="I105" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J105" t="str">
         <v>[[1,21204,100],[3,3019,100],[16,945,100],[19,945,100],[500001,11,50],[500002,11,50],[500101,11,10],[500102,11,10],[500003,10,50],[500103,10,10]]</v>
@@ -10713,13 +10709,13 @@
       </c>
       <c r="V105">
         <f>Y105/100</f>
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="W105">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="X105">
-        <v>2.59</v>
+        <v>1.56</v>
       </c>
       <c r="Y105">
         <v>560000000</v>
@@ -10772,7 +10768,7 @@
         <v>2</v>
       </c>
       <c r="I106" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J106" t="str">
         <v>[[1,21404,100],[3,3039,100],[16,947,100],[19,947,100],[500001,11,50],[500002,11,50],[500101,11,10],[500102,11,10],[500003,10,50],[500103,10,10]]</v>
@@ -10812,13 +10808,13 @@
       </c>
       <c r="V106">
         <f>Y106/100</f>
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="W106">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="X106">
-        <v>2.59</v>
+        <v>1.56</v>
       </c>
       <c r="Y106">
         <v>565000000</v>
@@ -10871,7 +10867,7 @@
         <v>3</v>
       </c>
       <c r="I107" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J107" t="str">
         <v>[[1,21604,100],[3,3059,100],[16,948,100],[19,948,100],[500001,11,50],[500002,11,50],[500101,11,10],[500102,11,10],[500003,10,50],[500103,10,10]]</v>
@@ -10911,13 +10907,13 @@
       </c>
       <c r="V107">
         <f>Y107/100</f>
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="W107">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="X107">
-        <v>2.59</v>
+        <v>1.56</v>
       </c>
       <c r="Y107">
         <v>620000000</v>
@@ -10970,7 +10966,7 @@
         <v>4</v>
       </c>
       <c r="I108" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J108" t="str">
         <v>[[1,21804,100],[3,3079,100],[16,949,100],[19,949,100],[500001,11,50],[500002,11,50],[500101,11,10],[500102,11,10],[500003,10,50],[500103,10,10]]</v>
@@ -11010,13 +11006,13 @@
       </c>
       <c r="V108">
         <f>Y108/100</f>
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="W108">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="X108">
-        <v>2.59</v>
+        <v>1.56</v>
       </c>
       <c r="Y108">
         <v>625000000</v>
@@ -11069,7 +11065,7 @@
         <v>1</v>
       </c>
       <c r="I109" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J109" t="str">
         <v>[[1,22004,100],[3,3099,100],[16,950,100],[19,950,100],[500001,11,50],[500002,11,50],[500101,11,10],[500102,11,10],[500003,11,50],[500103,11,10]]</v>
@@ -11109,13 +11105,13 @@
       </c>
       <c r="V109">
         <f>Y109/100</f>
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="W109">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="X109">
-        <v>2.59</v>
+        <v>1.56</v>
       </c>
       <c r="Y109">
         <v>640000000</v>
@@ -11168,7 +11164,7 @@
         <v>2</v>
       </c>
       <c r="I110" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J110" t="str">
         <v>[[1,22204,100],[3,3119,100],[16,952,100],[19,952,100],[500001,11,50],[500002,11,50],[500101,11,10],[500102,11,10],[500003,11,50],[500103,11,10]]</v>
@@ -11208,13 +11204,13 @@
       </c>
       <c r="V110">
         <f>Y110/100</f>
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="W110">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="X110">
-        <v>2.59</v>
+        <v>1.56</v>
       </c>
       <c r="Y110">
         <v>700000000</v>
@@ -11267,7 +11263,7 @@
         <v>3</v>
       </c>
       <c r="I111" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J111" t="str">
         <v>[[1,22404,100],[3,3139,100],[16,953,100],[19,953,100],[500001,12,50],[500002,11,50],[500101,12,10],[500102,11,10],[500003,11,50],[500103,11,10]]</v>
@@ -11307,13 +11303,13 @@
       </c>
       <c r="V111">
         <f>Y111/100</f>
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="W111">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="X111">
-        <v>2.59</v>
+        <v>1.56</v>
       </c>
       <c r="Y111">
         <v>705000000</v>
@@ -11366,7 +11362,7 @@
         <v>4</v>
       </c>
       <c r="I112" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J112" t="str">
         <v>[[1,22604,100],[3,3159,100],[16,954,100],[19,954,100],[500001,12,50],[500002,11,50],[500101,12,10],[500102,11,10],[500003,11,50],[500103,11,10]]</v>
@@ -11406,13 +11402,13 @@
       </c>
       <c r="V112">
         <f>Y112/100</f>
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="W112">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="X112">
-        <v>2.59</v>
+        <v>1.56</v>
       </c>
       <c r="Y112">
         <v>710000000</v>
@@ -11465,7 +11461,7 @@
         <v>1</v>
       </c>
       <c r="I113" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J113" t="str">
         <v>[[1,22804,100],[3,3179,100],[16,955,100],[19,955,100],[500001,12,50],[500002,11,50],[500101,12,10],[500102,11,10],[500003,11,50],[500103,11,10]]</v>
@@ -11505,13 +11501,13 @@
       </c>
       <c r="V113">
         <f>Y113/100</f>
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="W113">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="X113">
-        <v>2.59</v>
+        <v>1.56</v>
       </c>
       <c r="Y113">
         <v>780000000</v>
@@ -11564,7 +11560,7 @@
         <v>2</v>
       </c>
       <c r="I114" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J114" t="str">
         <v>[[1,23004,100],[3,3199,100],[16,956,100],[19,956,100],[500001,12,50],[500002,12,50],[500101,12,10],[500102,12,10],[500003,11,50],[500103,11,10]]</v>
@@ -11604,13 +11600,13 @@
       </c>
       <c r="V114">
         <f>Y114/100</f>
-        <v>1.11</v>
+        <v>2.23</v>
       </c>
       <c r="W114">
-        <v>1.03</v>
+        <v>2.05</v>
       </c>
       <c r="X114">
-        <v>3.42</v>
+        <v>2.05</v>
       </c>
       <c r="Y114">
         <v>800000000</v>
@@ -11663,7 +11659,7 @@
         <v>3</v>
       </c>
       <c r="I115" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J115" t="str">
         <v>[[1,23204,100],[3,3219,100],[16,958,100],[19,958,100],[500001,12,50],[500002,12,50],[500101,12,10],[500102,12,10],[500003,11,50],[500103,11,10]]</v>
@@ -11703,13 +11699,13 @@
       </c>
       <c r="V115">
         <f>Y115/100</f>
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="W115">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="X115">
-        <v>2.85</v>
+        <v>1.71</v>
       </c>
       <c r="Y115">
         <v>805000000</v>
@@ -11762,7 +11758,7 @@
         <v>4</v>
       </c>
       <c r="I116" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J116" t="str">
         <v>[[1,23404,100],[3,3239,100],[16,959,100],[19,959,100],[500001,12,50],[500002,12,50],[500101,12,10],[500102,12,10],[500003,11,50],[500103,11,10]]</v>
@@ -11802,13 +11798,13 @@
       </c>
       <c r="V116">
         <f>Y116/100</f>
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="W116">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="X116">
-        <v>2.85</v>
+        <v>1.71</v>
       </c>
       <c r="Y116">
         <v>820000000</v>
@@ -11861,7 +11857,7 @@
         <v>1</v>
       </c>
       <c r="I117" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J117" t="str">
         <v>[[1,23604,100],[3,3259,100],[16,960,100],[19,960,100],[500001,12,50],[500002,12,50],[500101,12,10],[500102,12,10],[500003,11,50],[500103,11,10]]</v>
@@ -11901,13 +11897,13 @@
       </c>
       <c r="V117">
         <f>Y117/100</f>
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="W117">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="X117">
-        <v>2.85</v>
+        <v>1.71</v>
       </c>
       <c r="Y117">
         <v>900000000</v>
@@ -11960,7 +11956,7 @@
         <v>2</v>
       </c>
       <c r="I118" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J118" t="str">
         <v>[[1,23805,100],[3,3279,100],[16,961,100],[19,961,100],[500001,12,50],[500002,12,50],[500101,12,10],[500102,12,10],[500003,11,50],[500103,11,10]]</v>
@@ -12000,13 +11996,13 @@
       </c>
       <c r="V118">
         <f>Y118/100</f>
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="W118">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="X118">
-        <v>2.85</v>
+        <v>1.71</v>
       </c>
       <c r="Y118">
         <v>920000000</v>
@@ -12059,7 +12055,7 @@
         <v>3</v>
       </c>
       <c r="I119" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J119" t="str">
         <v>[[1,24005,100],[3,3299,100],[16,962,100],[19,962,100],[500001,12,50],[500002,12,50],[500101,12,10],[500102,12,10],[500003,12,50],[500103,12,10]]</v>
@@ -12099,13 +12095,13 @@
       </c>
       <c r="V119">
         <f>Y119/100</f>
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="W119">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="X119">
-        <v>2.85</v>
+        <v>1.71</v>
       </c>
       <c r="Y119">
         <v>925000000</v>
@@ -12158,7 +12154,7 @@
         <v>4</v>
       </c>
       <c r="I120" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J120" t="str">
         <v>[[1,24205,100],[3,3319,100],[16,964,100],[19,964,100],[500001,12,50],[500002,12,50],[500101,12,10],[500102,12,10],[500003,12,50],[500103,12,10]]</v>
@@ -12198,13 +12194,13 @@
       </c>
       <c r="V120">
         <f>Y120/100</f>
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="W120">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="X120">
-        <v>2.85</v>
+        <v>1.71</v>
       </c>
       <c r="Y120">
         <v>1000000000</v>
@@ -12257,7 +12253,7 @@
         <v>1</v>
       </c>
       <c r="I121" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J121" t="str">
         <v>[[1,24405,100],[3,3339,100],[16,965,100],[19,965,100],[500001,13,50],[500002,12,50],[500101,13,10],[500102,12,10],[500003,12,50],[500103,12,10]]</v>
@@ -12297,13 +12293,13 @@
       </c>
       <c r="V121">
         <f>Y121/100</f>
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="W121">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="X121">
-        <v>2.85</v>
+        <v>1.71</v>
       </c>
       <c r="Y121">
         <v>1200000000</v>
@@ -12356,7 +12352,7 @@
         <v>2</v>
       </c>
       <c r="I122" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J122" t="str">
         <v>[[1,24605,100],[3,3359,100],[16,966,100],[19,966,100],[500001,13,50],[500002,12,50],[500101,13,10],[500102,12,10],[500003,12,50],[500103,12,10]]</v>
@@ -12396,13 +12392,13 @@
       </c>
       <c r="V122">
         <f>Y122/100</f>
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="W122">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="X122">
-        <v>2.85</v>
+        <v>1.71</v>
       </c>
       <c r="Y122">
         <v>1250000000</v>
@@ -12455,7 +12451,7 @@
         <v>3</v>
       </c>
       <c r="I123" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J123" t="str">
         <v>[[1,24805,100],[3,3379,100],[16,967,100],[19,967,100],[500001,13,50],[500002,12,50],[500101,13,10],[500102,12,10],[500003,12,50],[500103,12,10]]</v>
@@ -12495,13 +12491,13 @@
       </c>
       <c r="V123">
         <f>Y123/100</f>
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="W123">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="X123">
-        <v>2.85</v>
+        <v>1.71</v>
       </c>
       <c r="Y123">
         <v>1300000000</v>
@@ -12554,7 +12550,7 @@
         <v>4</v>
       </c>
       <c r="I124" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J124" t="str">
         <v>[[1,25005,100],[3,3399,100],[16,968,100],[19,968,100],[500001,13,50],[500002,13,50],[500101,13,10],[500102,13,10],[500003,12,50],[500103,12,10]]</v>
@@ -12594,13 +12590,13 @@
       </c>
       <c r="V124">
         <f>Y124/100</f>
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="W124">
-        <v>1.13</v>
+        <v>2.26</v>
       </c>
       <c r="X124">
-        <v>3.77</v>
+        <v>2.26</v>
       </c>
       <c r="Y124">
         <v>1350000000</v>
@@ -12653,7 +12649,7 @@
         <v>1</v>
       </c>
       <c r="I125" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J125" t="str">
         <v>[[1,25205,100],[3,3419,100],[16,969,100],[19,969,100],[500001,13,50],[500002,13,50],[500101,13,10],[500102,13,10],[500003,12,50],[500103,12,10]]</v>
@@ -12693,13 +12689,13 @@
       </c>
       <c r="V125">
         <f>Y125/100</f>
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="W125">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="X125">
-        <v>3.14</v>
+        <v>1.88</v>
       </c>
       <c r="Y125">
         <v>1400000000</v>
@@ -12752,7 +12748,7 @@
         <v>2</v>
       </c>
       <c r="I126" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J126" t="str">
         <v>[[1,25405,100],[3,3439,100],[16,970,100],[19,970,100],[500001,13,50],[500002,13,50],[500101,13,10],[500102,13,10],[500003,12,50],[500103,12,10]]</v>
@@ -12792,13 +12788,13 @@
       </c>
       <c r="V126">
         <f>Y126/100</f>
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="W126">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="X126">
-        <v>3.14</v>
+        <v>1.88</v>
       </c>
       <c r="Y126">
         <v>1450000000</v>
@@ -12851,7 +12847,7 @@
         <v>3</v>
       </c>
       <c r="I127" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J127" t="str">
         <v>[[1,25605,100],[3,3459,100],[16,971,100],[19,971,100],[500001,13,50],[500002,13,50],[500101,13,10],[500102,13,10],[500003,12,50],[500103,12,10]]</v>
@@ -12891,13 +12887,13 @@
       </c>
       <c r="V127">
         <f>Y127/100</f>
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="W127">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="X127">
-        <v>3.14</v>
+        <v>1.88</v>
       </c>
       <c r="Y127">
         <v>1500000000</v>
@@ -12950,7 +12946,7 @@
         <v>4</v>
       </c>
       <c r="I128" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J128" t="str">
         <v>[[1,25805,100],[3,3479,100],[16,972,100],[19,972,100],[500001,13,50],[500002,13,50],[500101,13,10],[500102,13,10],[500003,12,50],[500103,12,10]]</v>
@@ -12990,13 +12986,13 @@
       </c>
       <c r="V128">
         <f>Y128/100</f>
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="W128">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="X128">
-        <v>3.14</v>
+        <v>1.88</v>
       </c>
       <c r="Y128">
         <v>1550000000</v>
@@ -13049,7 +13045,7 @@
         <v>1</v>
       </c>
       <c r="I129" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J129" t="str">
         <v>[[1,26005,100],[3,3499,100],[16,974,100],[19,974,100],[500001,13,50],[500002,13,50],[500101,13,10],[500102,13,10],[500003,13,50],[500103,13,10]]</v>
@@ -13089,13 +13085,13 @@
       </c>
       <c r="V129">
         <f>Y129/100</f>
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="W129">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="X129">
-        <v>3.14</v>
+        <v>1.88</v>
       </c>
       <c r="Y129">
         <v>1600000000</v>
@@ -13148,7 +13144,7 @@
         <v>2</v>
       </c>
       <c r="I130" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J130" t="str">
         <v>[[1,26205,100],[3,3519,100],[16,975,100],[19,975,100],[500001,13,50],[500002,13,50],[500101,13,10],[500102,13,10],[500003,13,50],[500103,13,10]]</v>
@@ -13188,13 +13184,13 @@
       </c>
       <c r="V130">
         <f>Y130/100</f>
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="W130">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="X130">
-        <v>3.14</v>
+        <v>1.88</v>
       </c>
       <c r="Y130">
         <v>1650000000</v>
@@ -13247,7 +13243,7 @@
         <v>3</v>
       </c>
       <c r="I131" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J131" t="str">
         <v>[[1,26405,100],[3,3539,100],[16,976,100],[19,976,100],[500001,14,50],[500002,13,50],[500101,14,10],[500102,13,10],[500003,13,50],[500103,13,10]]</v>
@@ -13287,13 +13283,13 @@
       </c>
       <c r="V131">
         <f>Y131/100</f>
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="W131">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="X131">
-        <v>3.14</v>
+        <v>1.88</v>
       </c>
       <c r="Y131">
         <v>1700000000</v>
@@ -13346,7 +13342,7 @@
         <v>4</v>
       </c>
       <c r="I132" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J132" t="str">
         <v>[[1,26605,100],[3,3559,100],[16,977,100],[19,977,100],[500001,14,50],[500002,13,50],[500101,14,10],[500102,13,10],[500003,13,50],[500103,13,10]]</v>
@@ -13386,13 +13382,13 @@
       </c>
       <c r="V132">
         <f>Y132/100</f>
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="W132">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="X132">
-        <v>3.14</v>
+        <v>1.88</v>
       </c>
       <c r="Y132">
         <v>1750000000</v>
@@ -13445,7 +13441,7 @@
         <v>1</v>
       </c>
       <c r="I133" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J133" t="str">
         <v>[[1,26805,100],[3,3579,100],[16,978,100],[19,978,100],[500001,14,50],[500002,13,50],[500101,14,10],[500102,13,10],[500003,13,50],[500103,13,10]]</v>
@@ -13485,13 +13481,13 @@
       </c>
       <c r="V133">
         <f>Y133/100</f>
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="W133">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="X133">
-        <v>3.14</v>
+        <v>1.88</v>
       </c>
       <c r="Y133">
         <v>1800000000</v>
@@ -13544,7 +13540,7 @@
         <v>2</v>
       </c>
       <c r="I134" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J134" t="str">
         <v>[[1,27005,100],[3,3599,100],[16,979,100],[19,979,100],[500001,14,50],[500002,14,50],[500101,14,10],[500102,14,10],[500003,13,50],[500103,13,10]]</v>
@@ -13584,13 +13580,13 @@
       </c>
       <c r="V134">
         <f>Y134/100</f>
-        <v>1.35</v>
+        <v>2.69</v>
       </c>
       <c r="W134">
-        <v>1.24</v>
+        <v>2.49</v>
       </c>
       <c r="X134">
-        <v>4.14</v>
+        <v>2.49</v>
       </c>
       <c r="Y134">
         <v>1850000000</v>
@@ -13643,7 +13639,7 @@
         <v>3</v>
       </c>
       <c r="I135" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J135" t="str">
         <v>[[1,27205,100],[3,3619,100],[16,980,100],[19,980,100],[500001,14,50],[500002,14,50],[500101,14,10],[500102,14,10],[500003,13,50],[500103,13,10]]</v>
@@ -13683,13 +13679,13 @@
       </c>
       <c r="V135">
         <f>Y135/100</f>
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="W135">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="X135">
-        <v>3.45</v>
+        <v>2.07</v>
       </c>
       <c r="Y135">
         <v>1900000000</v>
@@ -13742,7 +13738,7 @@
         <v>4</v>
       </c>
       <c r="I136" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J136" t="str">
         <v>[[1,27405,100],[3,3639,100],[16,981,100],[19,981,100],[500001,14,50],[500002,14,50],[500101,14,10],[500102,14,10],[500003,13,50],[500103,13,10]]</v>
@@ -13782,13 +13778,13 @@
       </c>
       <c r="V136">
         <f>Y136/100</f>
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="W136">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="X136">
-        <v>3.45</v>
+        <v>2.07</v>
       </c>
       <c r="Y136">
         <v>1950000000</v>
@@ -13841,7 +13837,7 @@
         <v>1</v>
       </c>
       <c r="I137" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J137" t="str">
         <v>[[1,27605,100],[3,3659,100],[16,982,100],[19,982,100],[500001,14,50],[500002,14,50],[500101,14,10],[500102,14,10],[500003,13,50],[500103,13,10]]</v>
@@ -13881,13 +13877,13 @@
       </c>
       <c r="V137">
         <f>Y137/100</f>
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="W137">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="X137">
-        <v>3.45</v>
+        <v>2.07</v>
       </c>
       <c r="Y137">
         <v>2000000000</v>
@@ -13940,7 +13936,7 @@
         <v>2</v>
       </c>
       <c r="I138" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J138" t="str">
         <v>[[1,27805,100],[3,3679,100],[16,983,100],[19,983,100],[500001,14,50],[500002,14,50],[500101,14,10],[500102,14,10],[500003,13,50],[500103,13,10]]</v>
@@ -13980,13 +13976,13 @@
       </c>
       <c r="V138">
         <f>Y138/100</f>
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="W138">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="X138">
-        <v>3.45</v>
+        <v>2.07</v>
       </c>
       <c r="Y138">
         <v>2050000000</v>
@@ -14039,7 +14035,7 @@
         <v>3</v>
       </c>
       <c r="I139" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J139" t="str">
         <v>[[1,28005,100],[3,3699,100],[16,984,100],[19,984,100],[500001,14,50],[500002,14,50],[500101,14,10],[500102,14,10],[500003,14,50],[500103,14,10]]</v>
@@ -14079,13 +14075,13 @@
       </c>
       <c r="V139">
         <f>Y139/100</f>
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="W139">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="X139">
-        <v>3.45</v>
+        <v>2.07</v>
       </c>
       <c r="Y139">
         <v>2100000000</v>
@@ -14138,7 +14134,7 @@
         <v>4</v>
       </c>
       <c r="I140" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J140" t="str">
         <v>[[1,28205,100],[3,3719,100],[16,985,100],[19,985,100],[500001,14,50],[500002,14,50],[500101,14,10],[500102,14,10],[500003,14,50],[500103,14,10]]</v>
@@ -14178,13 +14174,13 @@
       </c>
       <c r="V140">
         <f>Y140/100</f>
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="W140">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="X140">
-        <v>3.45</v>
+        <v>2.07</v>
       </c>
       <c r="Y140">
         <v>2150000000</v>
@@ -14237,7 +14233,7 @@
         <v>1</v>
       </c>
       <c r="I141" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J141" t="str">
         <v>[[1,28405,100],[3,3739,100],[16,986,100],[19,986,100],[500001,15,50],[500002,14,50],[500101,15,10],[500102,14,10],[500003,14,50],[500103,14,10]]</v>
@@ -14277,13 +14273,13 @@
       </c>
       <c r="V141">
         <f>Y141/100</f>
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="W141">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="X141">
-        <v>3.45</v>
+        <v>2.07</v>
       </c>
       <c r="Y141">
         <v>2200000000</v>
@@ -14336,7 +14332,7 @@
         <v>2</v>
       </c>
       <c r="I142" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J142" t="str">
         <v>[[1,28605,100],[3,3759,100],[16,987,100],[19,987,100],[500001,15,50],[500002,14,50],[500101,15,10],[500102,14,10],[500003,14,50],[500103,14,10]]</v>
@@ -14376,13 +14372,13 @@
       </c>
       <c r="V142">
         <f>Y142/100</f>
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="W142">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="X142">
-        <v>3.45</v>
+        <v>2.07</v>
       </c>
       <c r="Y142">
         <v>2250000000</v>
@@ -14435,7 +14431,7 @@
         <v>3</v>
       </c>
       <c r="I143" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J143" t="str">
         <v>[[1,28806,100],[3,3779,100],[16,988,100],[19,988,100],[500001,15,50],[500002,14,50],[500101,15,10],[500102,14,10],[500003,14,50],[500103,14,10]]</v>
@@ -14475,13 +14471,13 @@
       </c>
       <c r="V143">
         <f>Y143/100</f>
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="W143">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="X143">
-        <v>3.45</v>
+        <v>2.07</v>
       </c>
       <c r="Y143">
         <v>2400000000</v>
@@ -14534,7 +14530,7 @@
         <v>4</v>
       </c>
       <c r="I144" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J144" t="str">
         <v>[[1,29006,100],[3,3799,100],[16,989,100],[19,989,100],[500001,15,50],[500002,15,50],[500101,15,10],[500102,15,10],[500003,14,50],[500103,14,10]]</v>
@@ -14574,13 +14570,13 @@
       </c>
       <c r="V144">
         <f>Y144/100</f>
-        <v>1.48</v>
+        <v>2.96</v>
       </c>
       <c r="W144">
-        <v>1.37</v>
+        <v>2.73</v>
       </c>
       <c r="X144">
-        <v>4.56</v>
+        <v>2.73</v>
       </c>
       <c r="Y144">
         <v>2450000000</v>
@@ -14633,7 +14629,7 @@
         <v>1</v>
       </c>
       <c r="I145" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J145" t="str">
         <v>[[1,29206,100],[3,3819,100],[16,990,100],[19,990,100],[500001,15,50],[500002,15,50],[500101,15,10],[500102,15,10],[500003,14,50],[500103,14,10]]</v>
@@ -14673,13 +14669,13 @@
       </c>
       <c r="V145">
         <f>Y145/100</f>
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="W145">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="X145">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="Y145">
         <v>2500000000</v>
@@ -14732,7 +14728,7 @@
         <v>2</v>
       </c>
       <c r="I146" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J146" t="str">
         <v>[[1,29406,100],[3,3839,100],[16,991,100],[19,991,100],[500001,15,50],[500002,15,50],[500101,15,10],[500102,15,10],[500003,14,50],[500103,14,10]]</v>
@@ -14772,13 +14768,13 @@
       </c>
       <c r="V146">
         <f>Y146/100</f>
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="W146">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="X146">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="Y146">
         <v>2550000000</v>
@@ -14831,7 +14827,7 @@
         <v>3</v>
       </c>
       <c r="I147" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J147" t="str">
         <v>[[1,29606,100],[3,3859,100],[16,992,100],[19,992,100],[500001,15,50],[500002,15,50],[500101,15,10],[500102,15,10],[500003,14,50],[500103,14,10]]</v>
@@ -14871,13 +14867,13 @@
       </c>
       <c r="V147">
         <f>Y147/100</f>
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="W147">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="X147">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="Y147">
         <v>2800000000</v>
@@ -14930,7 +14926,7 @@
         <v>4</v>
       </c>
       <c r="I148" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J148" t="str">
         <v>[[1,29806,100],[3,3879,100],[16,993,100],[19,993,100],[500001,15,50],[500002,15,50],[500101,15,10],[500102,15,10],[500003,14,50],[500103,14,10]]</v>
@@ -14970,13 +14966,13 @@
       </c>
       <c r="V148">
         <f>Y148/100</f>
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="W148">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="X148">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="Y148">
         <v>2850000000</v>
@@ -15029,7 +15025,7 @@
         <v>1</v>
       </c>
       <c r="I149" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J149" t="str">
         <v>[[1,30006,100],[3,3899,100],[16,994,100],[19,994,100],[500001,15,50],[500002,15,50],[500101,15,10],[500102,15,10],[500003,15,50],[500103,15,10]]</v>
@@ -15069,13 +15065,13 @@
       </c>
       <c r="V149">
         <f>Y149/100</f>
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="W149">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="X149">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="Y149">
         <v>2900000000</v>
@@ -15128,7 +15124,7 @@
         <v>2</v>
       </c>
       <c r="I150" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J150" t="str">
         <v>[[1,30206,100],[3,3919,100],[16,995,100],[19,995,100],[500001,15,50],[500002,15,50],[500101,15,10],[500102,15,10],[500003,15,50],[500103,15,10]]</v>
@@ -15168,13 +15164,13 @@
       </c>
       <c r="V150">
         <f>Y150/100</f>
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="W150">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="X150">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="Y150">
         <v>3000000000</v>
@@ -15227,7 +15223,7 @@
         <v>3</v>
       </c>
       <c r="I151" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J151" t="str">
         <v>[[1,30406,100],[3,3939,100],[16,996,100],[19,996,100],[500001,16,50],[500002,15,50],[500101,16,10],[500102,15,10],[500003,15,50],[500103,15,10]]</v>
@@ -15267,13 +15263,13 @@
       </c>
       <c r="V151">
         <f>Y151/100</f>
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="W151">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="X151">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="Y151">
         <v>3050000000</v>
@@ -15326,7 +15322,7 @@
         <v>4</v>
       </c>
       <c r="I152" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J152" t="str">
         <v>[[1,30606,100],[3,3959,100],[16,996,100],[19,996,100],[500001,16,50],[500002,15,50],[500101,16,10],[500102,15,10],[500003,15,50],[500103,15,10]]</v>
@@ -15366,13 +15362,13 @@
       </c>
       <c r="V152">
         <f>Y152/100</f>
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="W152">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="X152">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="Y152">
         <v>3100000000</v>
@@ -15425,7 +15421,7 @@
         <v>1</v>
       </c>
       <c r="I153" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J153" t="str">
         <v>[[1,30806,100],[3,3979,100],[16,997,100],[19,997,100],[500001,16,50],[500002,15,50],[500101,16,10],[500102,15,10],[500003,15,50],[500103,15,10]]</v>
@@ -15465,13 +15461,13 @@
       </c>
       <c r="V153">
         <f>Y153/100</f>
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="W153">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="X153">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="Y153">
         <v>3400000000</v>
@@ -15524,7 +15520,7 @@
         <v>2</v>
       </c>
       <c r="I154" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J154" t="str">
         <v>[[1,31006,100],[3,3999,100],[16,998,100],[19,998,100],[500001,16,50],[500002,16,50],[500101,16,10],[500102,16,10],[500003,15,50],[500103,15,10]]</v>
@@ -15564,13 +15560,13 @@
       </c>
       <c r="V154">
         <f>Y154/100</f>
-        <v>2.01</v>
+        <v>4.01</v>
       </c>
       <c r="W154">
-        <v>1.75</v>
+        <v>3.51</v>
       </c>
       <c r="X154">
-        <v>5.85</v>
+        <v>3.51</v>
       </c>
       <c r="Y154">
         <v>3450000000</v>
@@ -15623,7 +15619,7 @@
         <v>3</v>
       </c>
       <c r="I155" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J155" t="str">
         <v>[[1,31206,100],[3,4019,100],[16,999,100],[19,999,100],[500001,16,50],[500002,16,50],[500101,16,10],[500102,16,10],[500003,15,50],[500103,15,10]]</v>
@@ -15663,13 +15659,13 @@
       </c>
       <c r="V155">
         <f>Y155/100</f>
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="W155">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="X155">
-        <v>4.18</v>
+        <v>2.51</v>
       </c>
       <c r="Y155">
         <v>3500000000</v>
@@ -15722,7 +15718,7 @@
         <v>4</v>
       </c>
       <c r="I156" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J156" t="str">
         <v>[[1,31406,100],[3,4039,100],[16,1000,100],[19,1000,100],[500001,16,50],[500002,16,50],[500101,16,10],[500102,16,10],[500003,15,50],[500103,15,10]]</v>
@@ -15762,13 +15758,13 @@
       </c>
       <c r="V156">
         <f>Y156/100</f>
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="W156">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="X156">
-        <v>4.18</v>
+        <v>2.51</v>
       </c>
       <c r="Y156">
         <v>3550000000</v>
@@ -15821,7 +15817,7 @@
         <v>1</v>
       </c>
       <c r="I157" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J157" t="str">
         <v>[[1,31606,100],[3,4059,100],[16,1001,100],[19,1001,100],[500001,16,50],[500002,16,50],[500101,16,10],[500102,16,10],[500003,15,50],[500103,15,10]]</v>
@@ -15861,13 +15857,13 @@
       </c>
       <c r="V157">
         <f>Y157/100</f>
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="W157">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="X157">
-        <v>4.18</v>
+        <v>2.51</v>
       </c>
       <c r="Y157">
         <v>3800000000</v>
@@ -15920,7 +15916,7 @@
         <v>2</v>
       </c>
       <c r="I158" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J158" t="str">
         <v>[[1,31806,100],[3,4079,100],[16,1002,100],[19,1002,100],[500001,16,50],[500002,16,50],[500101,16,10],[500102,16,10],[500003,15,50],[500103,15,10]]</v>
@@ -15960,13 +15956,13 @@
       </c>
       <c r="V158">
         <f>Y158/100</f>
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="W158">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="X158">
-        <v>4.18</v>
+        <v>2.51</v>
       </c>
       <c r="Y158">
         <v>3850000000</v>
@@ -16019,7 +16015,7 @@
         <v>3</v>
       </c>
       <c r="I159" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J159" t="str">
         <v>[[1,32006,100],[3,4099,100],[16,1003,100],[19,1003,100],[500001,16,50],[500002,16,50],[500101,16,10],[500102,16,10],[500003,16,50],[500103,16,10]]</v>
@@ -16059,13 +16055,13 @@
       </c>
       <c r="V159">
         <f>Y159/100</f>
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="W159">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="X159">
-        <v>4.18</v>
+        <v>2.51</v>
       </c>
       <c r="Y159">
         <v>3900000000</v>
@@ -16118,7 +16114,7 @@
         <v>4</v>
       </c>
       <c r="I160" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J160" t="str">
         <v>[[1,32206,100],[3,4119,100],[16,1004,100],[19,1004,100],[500001,16,50],[500002,16,50],[500101,16,10],[500102,16,10],[500003,16,50],[500103,16,10]]</v>
@@ -16158,13 +16154,13 @@
       </c>
       <c r="V160">
         <f>Y160/100</f>
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="W160">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="X160">
-        <v>4.18</v>
+        <v>2.51</v>
       </c>
       <c r="Y160">
         <v>4200000000</v>
@@ -16217,7 +16213,7 @@
         <v>1</v>
       </c>
       <c r="I161" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J161" t="str">
         <v>[[1,32406,100],[3,4139,100],[16,1005,100],[19,1005,100],[500001,17,50],[500002,16,50],[500101,17,10],[500102,16,10],[500003,16,50],[500103,16,10]]</v>
@@ -16257,13 +16253,13 @@
       </c>
       <c r="V161">
         <f>Y161/100</f>
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="W161">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="X161">
-        <v>4.18</v>
+        <v>2.51</v>
       </c>
       <c r="Y161">
         <v>4250000000</v>
@@ -16316,7 +16312,7 @@
         <v>2</v>
       </c>
       <c r="I162" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J162" t="str">
         <v>[[1,32606,100],[3,4159,100],[16,1006,100],[19,1006,100],[500001,17,50],[500002,16,50],[500101,17,10],[500102,16,10],[500003,16,50],[500103,16,10]]</v>
@@ -16356,13 +16352,13 @@
       </c>
       <c r="V162">
         <f>Y162/100</f>
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="W162">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="X162">
-        <v>4.18</v>
+        <v>2.51</v>
       </c>
       <c r="Y162">
         <v>4300000000</v>
@@ -16415,7 +16411,7 @@
         <v>3</v>
       </c>
       <c r="I163" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J163" t="str">
         <v>[[1,32806,100],[3,4179,100],[16,1006,100],[19,1006,100],[500001,17,50],[500002,16,50],[500101,17,10],[500102,16,10],[500003,16,50],[500103,16,10]]</v>
@@ -16455,13 +16451,13 @@
       </c>
       <c r="V163">
         <f>Y163/100</f>
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="W163">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="X163">
-        <v>4.18</v>
+        <v>2.51</v>
       </c>
       <c r="Y163">
         <v>4600000000</v>
@@ -16514,7 +16510,7 @@
         <v>4</v>
       </c>
       <c r="I164" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J164" t="str">
         <v>[[1,33006,100],[3,4199,100],[16,1007,100],[19,1007,100],[500001,17,50],[500002,17,50],[500101,17,10],[500102,17,10],[500003,16,50],[500103,16,10]]</v>
@@ -16554,13 +16550,13 @@
       </c>
       <c r="V164">
         <f>Y164/100</f>
-        <v>1.79</v>
+        <v>3.58</v>
       </c>
       <c r="W164">
-        <v>1.65</v>
+        <v>3.31</v>
       </c>
       <c r="X164">
-        <v>5.51</v>
+        <v>3.31</v>
       </c>
       <c r="Y164">
         <v>4800000000</v>
@@ -16613,7 +16609,7 @@
         <v>1</v>
       </c>
       <c r="I165" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J165" t="str">
         <v>[[1,33206,100],[3,4219,100],[16,1008,100],[19,1008,100],[500001,17,50],[500002,17,50],[500101,17,10],[500102,17,10],[500003,16,50],[500103,16,10]]</v>
@@ -16653,13 +16649,13 @@
       </c>
       <c r="V165">
         <f>Y165/100</f>
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="W165">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="X165">
-        <v>4.59</v>
+        <v>2.76</v>
       </c>
       <c r="Y165">
         <v>4850000000</v>
@@ -16712,7 +16708,7 @@
         <v>2</v>
       </c>
       <c r="I166" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J166" t="str">
         <v>[[1,33406,100],[3,4239,100],[16,1009,100],[19,1009,100],[500001,17,50],[500002,17,50],[500101,17,10],[500102,17,10],[500003,16,50],[500103,16,10]]</v>
@@ -16752,13 +16748,13 @@
       </c>
       <c r="V166">
         <f>Y166/100</f>
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="W166">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="X166">
-        <v>4.59</v>
+        <v>2.76</v>
       </c>
       <c r="Y166">
         <v>4900000000</v>
@@ -16811,7 +16807,7 @@
         <v>3</v>
       </c>
       <c r="I167" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J167" t="str">
         <v>[[1,33606,100],[3,4259,100],[16,1010,100],[19,1010,100],[500001,17,50],[500002,17,50],[500101,17,10],[500102,17,10],[500003,16,50],[500103,16,10]]</v>
@@ -16851,13 +16847,13 @@
       </c>
       <c r="V167">
         <f>Y167/100</f>
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="W167">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="X167">
-        <v>4.59</v>
+        <v>2.76</v>
       </c>
       <c r="Y167">
         <v>5400000000</v>
@@ -16910,7 +16906,7 @@
         <v>4</v>
       </c>
       <c r="I168" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J168" t="str">
         <v>[[1,33807,100],[3,4279,100],[16,1011,100],[19,1011,100],[500001,17,50],[500002,17,50],[500101,17,10],[500102,17,10],[500003,16,50],[500103,16,10]]</v>
@@ -16950,13 +16946,13 @@
       </c>
       <c r="V168">
         <f>Y168/100</f>
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="W168">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="X168">
-        <v>4.59</v>
+        <v>2.76</v>
       </c>
       <c r="Y168">
         <v>5450000000</v>
@@ -17009,7 +17005,7 @@
         <v>1</v>
       </c>
       <c r="I169" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J169" t="str">
         <v>[[1,34007,100],[3,4299,100],[16,1012,100],[19,1012,100],[500001,17,50],[500002,17,50],[500101,17,10],[500102,17,10],[500003,17,50],[500103,17,10]]</v>
@@ -17049,13 +17045,13 @@
       </c>
       <c r="V169">
         <f>Y169/100</f>
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="W169">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="X169">
-        <v>4.59</v>
+        <v>2.76</v>
       </c>
       <c r="Y169">
         <v>5500000000</v>
@@ -17108,7 +17104,7 @@
         <v>2</v>
       </c>
       <c r="I170" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J170" t="str">
         <v>[[1,34207,100],[3,4319,100],[16,1012,100],[19,1012,100],[500001,17,50],[500002,17,50],[500101,17,10],[500102,17,10],[500003,17,50],[500103,17,10]]</v>
@@ -17148,13 +17144,13 @@
       </c>
       <c r="V170">
         <f>Y170/100</f>
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="W170">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="X170">
-        <v>4.59</v>
+        <v>2.76</v>
       </c>
       <c r="Y170">
         <v>6000000000</v>
@@ -17207,7 +17203,7 @@
         <v>3</v>
       </c>
       <c r="I171" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J171" t="str">
         <v>[[1,34407,100],[3,4339,100],[16,1013,100],[19,1013,100],[500001,18,50],[500002,17,50],[500101,18,10],[500102,17,10],[500003,17,50],[500103,17,10]]</v>
@@ -17247,13 +17243,13 @@
       </c>
       <c r="V171">
         <f>Y171/100</f>
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="W171">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="X171">
-        <v>4.59</v>
+        <v>2.76</v>
       </c>
       <c r="Y171">
         <v>6050000000</v>
@@ -17306,7 +17302,7 @@
         <v>4</v>
       </c>
       <c r="I172" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J172" t="str">
         <v>[[1,34607,100],[3,4359,100],[16,1014,100],[19,1014,100],[500001,18,50],[500002,17,50],[500101,18,10],[500102,17,10],[500003,17,50],[500103,17,10]]</v>
@@ -17346,13 +17342,13 @@
       </c>
       <c r="V172">
         <f>Y172/100</f>
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="W172">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="X172">
-        <v>4.59</v>
+        <v>2.76</v>
       </c>
       <c r="Y172">
         <v>6100000000</v>
@@ -17405,7 +17401,7 @@
         <v>1</v>
       </c>
       <c r="I173" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J173" t="str">
         <v>[[1,34807,100],[3,4379,100],[16,1015,100],[19,1015,100],[500001,18,50],[500002,17,50],[500101,18,10],[500102,17,10],[500003,17,50],[500103,17,10]]</v>
@@ -17445,13 +17441,13 @@
       </c>
       <c r="V173">
         <f>Y173/100</f>
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="W173">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="X173">
-        <v>4.59</v>
+        <v>2.76</v>
       </c>
       <c r="Y173">
         <v>6400000000</v>
@@ -17504,7 +17500,7 @@
         <v>2</v>
       </c>
       <c r="I174" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J174" t="str">
         <v>[[1,35007,100],[3,4399,100],[16,1016,100],[19,1016,100],[500001,18,50],[500002,18,50],[500101,18,10],[500102,18,10],[500003,17,50],[500103,17,10]]</v>
@@ -17544,13 +17540,13 @@
       </c>
       <c r="V174">
         <f>Y174/100</f>
-        <v>1.97</v>
+        <v>3.94</v>
       </c>
       <c r="W174">
-        <v>1.82</v>
+        <v>3.64</v>
       </c>
       <c r="X174">
-        <v>6.07</v>
+        <v>3.64</v>
       </c>
       <c r="Y174">
         <v>6600000000</v>
@@ -17603,7 +17599,7 @@
         <v>3</v>
       </c>
       <c r="I175" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J175" t="str">
         <v>[[1,35207,100],[3,4419,100],[16,1017,100],[19,1017,100],[500001,18,50],[500002,18,50],[500101,18,10],[500102,18,10],[500003,17,50],[500103,17,10]]</v>
@@ -17643,13 +17639,13 @@
       </c>
       <c r="V175">
         <f>Y175/100</f>
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="W175">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="X175">
-        <v>5.05</v>
+        <v>3.03</v>
       </c>
       <c r="Y175">
         <v>7000000000</v>
@@ -17702,7 +17698,7 @@
         <v>4</v>
       </c>
       <c r="I176" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J176" t="str">
         <v>[[1,35407,100],[3,4439,100],[16,1017,100],[19,1017,100],[500001,18,50],[500002,18,50],[500101,18,10],[500102,18,10],[500003,17,50],[500103,17,10]]</v>
@@ -17742,13 +17738,13 @@
       </c>
       <c r="V176">
         <f>Y176/100</f>
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="W176">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="X176">
-        <v>5.05</v>
+        <v>3.03</v>
       </c>
       <c r="Y176">
         <v>7200000000</v>
@@ -17801,7 +17797,7 @@
         <v>1</v>
       </c>
       <c r="I177" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J177" t="str">
         <v>[[1,35607,100],[3,4459,100],[16,1018,100],[19,1018,100],[500001,18,50],[500002,18,50],[500101,18,10],[500102,18,10],[500003,17,50],[500103,17,10]]</v>
@@ -17841,13 +17837,13 @@
       </c>
       <c r="V177">
         <f>Y177/100</f>
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="W177">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="X177">
-        <v>5.05</v>
+        <v>3.03</v>
       </c>
       <c r="Y177">
         <v>9200000000</v>
@@ -17900,7 +17896,7 @@
         <v>2</v>
       </c>
       <c r="I178" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J178" t="str">
         <v>[[1,35807,100],[3,4479,100],[16,1019,100],[19,1019,100],[500001,18,50],[500002,18,50],[500101,18,10],[500102,18,10],[500003,17,50],[500103,17,10]]</v>
@@ -17940,13 +17936,13 @@
       </c>
       <c r="V178">
         <f>Y178/100</f>
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="W178">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="X178">
-        <v>5.05</v>
+        <v>3.03</v>
       </c>
       <c r="Y178">
         <v>9400000000</v>
@@ -17999,7 +17995,7 @@
         <v>3</v>
       </c>
       <c r="I179" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J179" t="str">
         <v>[[1,36007,100],[3,4499,100],[16,1020,100],[19,1020,100],[500001,18,50],[500002,18,50],[500101,18,10],[500102,18,10],[500003,18,50],[500103,18,10]]</v>
@@ -18039,13 +18035,13 @@
       </c>
       <c r="V179">
         <f>Y179/100</f>
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="W179">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="X179">
-        <v>5.05</v>
+        <v>3.03</v>
       </c>
       <c r="Y179">
         <v>9800000000</v>
@@ -18098,7 +18094,7 @@
         <v>4</v>
       </c>
       <c r="I180" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J180" t="str">
         <v>[[1,36207,100],[3,4519,100],[16,1021,100],[19,1021,100],[500001,18,50],[500002,18,50],[500101,18,10],[500102,18,10],[500003,18,50],[500103,18,10]]</v>
@@ -18138,13 +18134,13 @@
       </c>
       <c r="V180">
         <f>Y180/100</f>
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="W180">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="X180">
-        <v>5.05</v>
+        <v>3.03</v>
       </c>
       <c r="Y180">
         <v>12000000000</v>
@@ -18197,7 +18193,7 @@
         <v>1</v>
       </c>
       <c r="I181" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J181" t="str">
         <v>[[1,36407,100],[3,4539,100],[16,1021,100],[19,1021,100],[500001,19,50],[500002,18,50],[500101,19,10],[500102,18,10],[500003,18,50],[500103,18,10]]</v>
@@ -18237,13 +18233,13 @@
       </c>
       <c r="V181">
         <f>Y181/100</f>
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="W181">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="X181">
-        <v>5.05</v>
+        <v>3.03</v>
       </c>
       <c r="Y181">
         <v>12500000000</v>
@@ -18296,7 +18292,7 @@
         <v>2</v>
       </c>
       <c r="I182" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J182" t="str">
         <v>[[1,36607,100],[3,4559,100],[16,1022,100],[19,1022,100],[500001,19,50],[500002,18,50],[500101,19,10],[500102,18,10],[500003,18,50],[500103,18,10]]</v>
@@ -18336,13 +18332,13 @@
       </c>
       <c r="V182">
         <f>Y182/100</f>
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="W182">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="X182">
-        <v>5.05</v>
+        <v>3.03</v>
       </c>
       <c r="Y182">
         <v>13000000000</v>
@@ -18395,7 +18391,7 @@
         <v>3</v>
       </c>
       <c r="I183" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J183" t="str">
         <v>[[1,36807,100],[3,4579,100],[16,1023,100],[19,1023,100],[500001,19,50],[500002,18,50],[500101,19,10],[500102,18,10],[500003,18,50],[500103,18,10]]</v>
@@ -18435,13 +18431,13 @@
       </c>
       <c r="V183">
         <f>Y183/100</f>
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="W183">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="X183">
-        <v>5.05</v>
+        <v>3.03</v>
       </c>
       <c r="Y183">
         <v>16000000000</v>
@@ -18494,7 +18490,7 @@
         <v>4</v>
       </c>
       <c r="I184" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J184" t="str">
         <v>[[1,37007,100],[3,4599,100],[16,1024,100],[19,1024,100],[500001,19,50],[500002,19,50],[500101,19,10],[500102,19,10],[500003,18,50],[500103,18,10]]</v>
@@ -18534,13 +18530,13 @@
       </c>
       <c r="V184">
         <f>Y184/100</f>
-        <v>2.17</v>
+        <v>4.34</v>
       </c>
       <c r="W184">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X184">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="Y184">
         <v>16500000000</v>
@@ -18593,7 +18589,7 @@
         <v>1</v>
       </c>
       <c r="I185" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J185" t="str">
         <v>[[1,37207,100],[3,4619,100],[16,1025,100],[19,1025,100],[500001,19,50],[500002,19,50],[500101,19,10],[500102,19,10],[500003,18,50],[500103,18,10]]</v>
@@ -18633,13 +18629,13 @@
       </c>
       <c r="V185">
         <f>Y185/100</f>
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="W185">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="X185">
-        <v>5.56</v>
+        <v>3.34</v>
       </c>
       <c r="Y185">
         <v>17000000000</v>
@@ -18692,7 +18688,7 @@
         <v>2</v>
       </c>
       <c r="I186" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J186" t="str">
         <v>[[1,37407,100],[3,4639,100],[16,1025,100],[19,1025,100],[500001,19,50],[500002,19,50],[500101,19,10],[500102,19,10],[500003,18,50],[500103,18,10]]</v>
@@ -18732,13 +18728,13 @@
       </c>
       <c r="V186">
         <f>Y186/100</f>
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="W186">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="X186">
-        <v>5.56</v>
+        <v>3.34</v>
       </c>
       <c r="Y186">
         <v>17500000000</v>
@@ -18791,7 +18787,7 @@
         <v>3</v>
       </c>
       <c r="I187" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J187" t="str">
         <v>[[1,37607,100],[3,4659,100],[16,1026,100],[19,1026,100],[500001,19,50],[500002,19,50],[500101,19,10],[500102,19,10],[500003,18,50],[500103,18,10]]</v>
@@ -18831,13 +18827,13 @@
       </c>
       <c r="V187">
         <f>Y187/100</f>
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="W187">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="X187">
-        <v>5.56</v>
+        <v>3.34</v>
       </c>
       <c r="Y187">
         <v>24000000000</v>
@@ -18890,7 +18886,7 @@
         <v>4</v>
       </c>
       <c r="I188" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J188" t="str">
         <v>[[1,37807,100],[3,4679,100],[16,1027,100],[19,1027,100],[500001,19,50],[500002,19,50],[500101,19,10],[500102,19,10],[500003,18,50],[500103,18,10]]</v>
@@ -18930,13 +18926,13 @@
       </c>
       <c r="V188">
         <f>Y188/100</f>
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="W188">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="X188">
-        <v>5.56</v>
+        <v>3.34</v>
       </c>
       <c r="Y188">
         <v>24500000000</v>
@@ -18989,7 +18985,7 @@
         <v>1</v>
       </c>
       <c r="I189" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J189" t="str">
         <v>[[1,38007,100],[3,4699,100],[16,1028,100],[19,1028,100],[500001,19,50],[500002,19,50],[500101,19,10],[500102,19,10],[500003,19,50],[500103,19,10]]</v>
@@ -19029,13 +19025,13 @@
       </c>
       <c r="V189">
         <f>Y189/100</f>
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="W189">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="X189">
-        <v>5.56</v>
+        <v>3.34</v>
       </c>
       <c r="Y189">
         <v>26000000000</v>
@@ -19088,7 +19084,7 @@
         <v>2</v>
       </c>
       <c r="I190" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J190" t="str">
         <v>[[1,38207,100],[3,4719,100],[16,1028,100],[19,1028,100],[500001,19,50],[500002,19,50],[500101,19,10],[500102,19,10],[500003,19,50],[500103,19,10]]</v>
@@ -19128,13 +19124,13 @@
       </c>
       <c r="V190">
         <f>Y190/100</f>
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="W190">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="X190">
-        <v>5.56</v>
+        <v>3.34</v>
       </c>
       <c r="Y190">
         <v>32000000000</v>
@@ -19187,7 +19183,7 @@
         <v>3</v>
       </c>
       <c r="I191" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J191" t="str">
         <v>[[1,38407,100],[3,4739,100],[16,1029,100],[19,1029,100],[500001,20,50],[500002,19,50],[500101,20,10],[500102,19,10],[500003,19,50],[500103,19,10]]</v>
@@ -19227,13 +19223,13 @@
       </c>
       <c r="V191">
         <f>Y191/100</f>
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="W191">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="X191">
-        <v>5.56</v>
+        <v>3.34</v>
       </c>
       <c r="Y191">
         <v>32500000000</v>
@@ -19286,7 +19282,7 @@
         <v>4</v>
       </c>
       <c r="I192" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J192" t="str">
         <v>[[1,38607,100],[3,4759,100],[16,1030,100],[19,1030,100],[500001,20,50],[500002,19,50],[500101,20,10],[500102,19,10],[500003,19,50],[500103,19,10]]</v>
@@ -19326,13 +19322,13 @@
       </c>
       <c r="V192">
         <f>Y192/100</f>
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="W192">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="X192">
-        <v>5.56</v>
+        <v>3.34</v>
       </c>
       <c r="Y192">
         <v>34000000000</v>
@@ -19385,7 +19381,7 @@
         <v>1</v>
       </c>
       <c r="I193" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J193" t="str">
         <v>[[1,38808,100],[3,4778,100],[16,1031,100],[19,1031,100],[500001,20,50],[500002,19,50],[500101,20,10],[500102,19,10],[500003,19,50],[500103,19,10]]</v>
@@ -19425,13 +19421,13 @@
       </c>
       <c r="V193">
         <f>Y193/100</f>
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="W193">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="X193">
-        <v>5.56</v>
+        <v>3.34</v>
       </c>
       <c r="Y193">
         <v>40000000000</v>
@@ -19484,7 +19480,7 @@
         <v>2</v>
       </c>
       <c r="I194" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J194" t="str">
         <v>[[1,39008,100],[3,4798,100],[16,1031,100],[19,1031,100],[500001,20,50],[500002,20,50],[500101,20,10],[500102,20,10],[500003,19,50],[500103,19,10]]</v>
@@ -19524,13 +19520,13 @@
       </c>
       <c r="V194">
         <f>Y194/100</f>
-        <v>2.39</v>
+        <v>4.77</v>
       </c>
       <c r="W194">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="X194">
-        <v>7.34</v>
+        <v>4.4</v>
       </c>
       <c r="Y194">
         <v>42000000000</v>
@@ -19583,7 +19579,7 @@
         <v>3</v>
       </c>
       <c r="I195" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J195" t="str">
         <v>[[1,39208,100],[3,4818,100],[16,1032,100],[19,1032,100],[500001,20,50],[500002,20,50],[500101,20,10],[500102,20,10],[500003,19,50],[500103,19,10]]</v>
@@ -19623,13 +19619,13 @@
       </c>
       <c r="V195">
         <f>Y195/100</f>
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="W195">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="X195">
-        <v>6.12</v>
+        <v>3.67</v>
       </c>
       <c r="Y195">
         <v>48000000000</v>
@@ -19682,7 +19678,7 @@
         <v>4</v>
       </c>
       <c r="I196" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J196" t="str">
         <v>[[1,39408,100],[3,4838,100],[16,1033,100],[19,1033,100],[500001,20,50],[500002,20,50],[500101,20,10],[500102,20,10],[500003,19,50],[500103,19,10]]</v>
@@ -19722,13 +19718,13 @@
       </c>
       <c r="V196">
         <f>Y196/100</f>
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="W196">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="X196">
-        <v>6.12</v>
+        <v>3.67</v>
       </c>
       <c r="Y196">
         <v>56000000000</v>
@@ -19781,7 +19777,7 @@
         <v>1</v>
       </c>
       <c r="I197" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J197" t="str">
         <v>[[1,39608,100],[3,4858,100],[16,1034,100],[19,1034,100],[500001,20,50],[500002,20,50],[500101,20,10],[500102,20,10],[500003,19,50],[500103,19,10]]</v>
@@ -19821,13 +19817,13 @@
       </c>
       <c r="V197">
         <f>Y197/100</f>
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="W197">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="X197">
-        <v>6.12</v>
+        <v>3.67</v>
       </c>
       <c r="Y197">
         <v>120000000000</v>
@@ -19880,7 +19876,7 @@
         <v>2</v>
       </c>
       <c r="I198" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J198" t="str">
         <v>[[1,39808,100],[3,4878,100],[16,1034,100],[19,1034,100],[500001,20,50],[500002,20,50],[500101,20,10],[500102,20,10],[500003,19,50],[500103,19,10]]</v>
@@ -19920,13 +19916,13 @@
       </c>
       <c r="V198">
         <f>Y198/100</f>
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="W198">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="X198">
-        <v>6.12</v>
+        <v>3.67</v>
       </c>
       <c r="Y198">
         <v>125000000000</v>
@@ -19979,7 +19975,7 @@
         <v>3</v>
       </c>
       <c r="I199" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J199" t="str">
         <v>[[1,40008,100],[3,4898,100],[16,1035,100],[19,1035,100],[500001,20,50],[500002,20,50],[500101,20,10],[500102,20,10],[500003,20,50],[500103,20,10]]</v>
@@ -20019,13 +20015,13 @@
       </c>
       <c r="V199">
         <f>Y199/100</f>
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="W199">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="X199">
-        <v>6.12</v>
+        <v>3.67</v>
       </c>
       <c r="Y199">
         <v>130000000000</v>
@@ -20078,7 +20074,7 @@
         <v>4</v>
       </c>
       <c r="I200" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J200" t="str">
         <v>[[1,40208,100],[3,4918,100],[16,1036,100],[19,1036,100],[500001,20,50],[500002,20,50],[500101,20,10],[500102,20,10],[500003,20,50],[500103,20,10]]</v>
@@ -20118,13 +20114,13 @@
       </c>
       <c r="V200">
         <f>Y200/100</f>
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="W200">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="X200">
-        <v>6.12</v>
+        <v>3.67</v>
       </c>
       <c r="Y200">
         <v>180000000000</v>
@@ -20177,7 +20173,7 @@
         <v>1</v>
       </c>
       <c r="I201" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J201" t="str">
         <v>[[1,40408,100],[3,4938,100],[16,1037,100],[19,1037,100],[500001,21,50],[500002,20,50],[500101,21,10],[500102,20,10],[500003,20,50],[500103,20,10]]</v>
@@ -20217,13 +20213,13 @@
       </c>
       <c r="V201">
         <f>Y201/100</f>
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="W201">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="X201">
-        <v>6.12</v>
+        <v>3.67</v>
       </c>
       <c r="Y201">
         <v>185000000000</v>
@@ -20276,7 +20272,7 @@
         <v>2</v>
       </c>
       <c r="I202" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J202" t="str">
         <v>[[1,40608,100],[3,4958,100],[16,1037,100],[19,1037,100],[500001,21,50],[500002,20,50],[500101,21,10],[500102,20,10],[500003,20,50],[500103,20,10]]</v>
@@ -20316,13 +20312,13 @@
       </c>
       <c r="V202">
         <f>Y202/100</f>
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="W202">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="X202">
-        <v>6.12</v>
+        <v>3.67</v>
       </c>
       <c r="Y202">
         <v>190000000000</v>
@@ -20375,7 +20371,7 @@
         <v>3</v>
       </c>
       <c r="I203" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J203" t="str">
         <v>[[1,40808,100],[3,4978,100],[16,1038,100],[19,1038,100],[500001,21,50],[500002,20,50],[500101,21,10],[500102,20,10],[500003,20,50],[500103,20,10]]</v>
@@ -20415,13 +20411,13 @@
       </c>
       <c r="V203">
         <f>Y203/100</f>
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="W203">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="X203">
-        <v>6.12</v>
+        <v>3.67</v>
       </c>
       <c r="Y203">
         <v>240000000000</v>
@@ -20474,7 +20470,7 @@
         <v>4</v>
       </c>
       <c r="I204" t="str">
-        <v>[5,3]</v>
+        <v>[7,5]</v>
       </c>
       <c r="J204" t="str">
         <v>[[1,41008,100],[3,4998,100],[16,1039,100],[19,1039,100],[500001,21,50],[500002,21,50],[500101,21,10],[500102,21,10],[500003,20,50],[500103,20,10]]</v>
@@ -20514,13 +20510,13 @@
       </c>
       <c r="V204">
         <f>Y204/100</f>
-        <v>3.23</v>
+        <v>6.46</v>
       </c>
       <c r="W204">
-        <v>2.83</v>
+        <v>5.65</v>
       </c>
       <c r="X204">
-        <v>9.42</v>
+        <v>5.65</v>
       </c>
       <c r="Y204">
         <v>260000000000</v>
